--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -651,7 +651,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -4786,22 +4786,18 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>12370680</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18829</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -5190,22 +5186,18 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>12333720</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>18773</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -5594,22 +5586,18 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>12296760</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>18717</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5998,22 +5986,18 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>12259800</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>18660</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -6402,22 +6386,18 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>12223680</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>18605</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -6806,22 +6786,18 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>12186720</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>18549</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -7210,22 +7186,18 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>12150600</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18494</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -7614,22 +7586,18 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>12150600</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>18494</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -8018,22 +7986,18 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>12078360</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>18384</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -10054,22 +10018,18 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>11922120</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>18146</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -10458,22 +10418,18 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>11897760</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>18109</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -10862,22 +10818,18 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>11874240</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>18073</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N152" s="3" t="inlineStr">
@@ -11402,22 +11354,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>7568400</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>17935</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11806,22 +11754,18 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>7545720</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>17881</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N166" s="3" t="inlineStr">
@@ -12210,22 +12154,18 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>7523040</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>17827</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -12478,22 +12418,18 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>11779320</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>17929</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -12610,22 +12546,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>7485240</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>17738</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12878,22 +12810,18 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>11755800</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>17893</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -13010,22 +12938,18 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>7433160</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>17614</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
@@ -13278,22 +13202,18 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>11732280</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>17857</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -13410,22 +13330,18 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>7321440</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>17349</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13814,22 +13730,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>7138320</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>16915</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -14218,22 +14130,18 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>7138320</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>16915</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N202" s="3" t="inlineStr">
@@ -14622,22 +14530,18 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K208" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L208" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>7095480</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>16814</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14890,22 +14794,18 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>11639040</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>17715</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
@@ -15022,22 +14922,18 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>7074480</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>16764</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -15290,22 +15186,18 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>11615520</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>17680</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -15422,22 +15314,18 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>7032480</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>16665</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -15690,22 +15578,18 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>11607120</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>17667</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -16162,22 +16046,18 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>7830480</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>18733</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -16226,22 +16106,18 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>7807800</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>18679</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -16290,22 +16166,18 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7784280</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>18623</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -16830,22 +16702,18 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>7760760</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>18566</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -17370,22 +17238,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>7737240</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>18510</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -17910,22 +17774,18 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>7714560</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>18456</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -18450,22 +18310,18 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>7714560</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>18456</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
@@ -18990,22 +18846,18 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>7668360</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>18345</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
@@ -19530,22 +19382,18 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>7645680</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>18291</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -19662,22 +19510,18 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>5902680</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>19290</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
@@ -20066,22 +19910,18 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>7623000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>18237</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N289" s="3" t="inlineStr">
@@ -20198,22 +20038,18 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>5885040</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>19232</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
@@ -20602,22 +20438,18 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>7599480</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>18181</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N297" s="3" t="inlineStr">
@@ -20734,22 +20566,18 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K299" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L299" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K299" s="5" t="n">
+        <v>5867400</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>19175</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N299" s="3" t="inlineStr">
@@ -21138,22 +20966,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K305" s="5" t="n">
+        <v>7576800</v>
+      </c>
+      <c r="L305" s="5" t="n">
+        <v>18126</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -21270,22 +21094,18 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K307" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L307" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K307" s="5" t="n">
+        <v>5849760</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>19117</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N307" s="3" t="inlineStr">
@@ -21674,22 +21494,18 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K313" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L313" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K313" s="5" t="n">
+        <v>7554120</v>
+      </c>
+      <c r="L313" s="5" t="n">
+        <v>18072</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N313" s="3" t="inlineStr">
@@ -21806,22 +21622,18 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K315" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L315" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K315" s="5" t="n">
+        <v>5832120</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>19059</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N315" s="3" t="inlineStr">
@@ -22210,22 +22022,18 @@
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K321" s="5" t="n">
+        <v>7531440</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>18018</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N321" s="3" t="inlineStr">
@@ -22342,22 +22150,18 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>5814480</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>19002</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
@@ -22746,22 +22550,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K329" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L329" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K329" s="5" t="n">
+        <v>7509600</v>
+      </c>
+      <c r="L329" s="5" t="n">
+        <v>17966</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -22878,22 +22678,18 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K331" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L331" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K331" s="5" t="n">
+        <v>5797680</v>
+      </c>
+      <c r="L331" s="5" t="n">
+        <v>18947</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N331" s="3" t="inlineStr">
@@ -23282,22 +23078,18 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L337" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>7509600</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>17966</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N337" s="3" t="inlineStr">
@@ -23414,22 +23206,18 @@
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>5797680</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>18947</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N339" s="3" t="inlineStr">
@@ -23818,22 +23606,18 @@
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K345" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L345" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K345" s="5" t="n">
+        <v>7464240</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>17857</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N345" s="3" t="inlineStr">
@@ -23950,22 +23734,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K347" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L347" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K347" s="5" t="n">
+        <v>5763240</v>
+      </c>
+      <c r="L347" s="5" t="n">
+        <v>18834</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -24354,22 +24134,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K353" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L353" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K353" s="5" t="n">
+        <v>7460880</v>
+      </c>
+      <c r="L353" s="5" t="n">
+        <v>17849</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -24894,22 +24670,18 @@
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K361" s="5" t="n">
+        <v>7445760</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>17813</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N361" s="3" t="inlineStr">
@@ -25978,22 +25750,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K377" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L377" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K377" s="5" t="n">
+        <v>7430640</v>
+      </c>
+      <c r="L377" s="5" t="n">
+        <v>17777</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -26314,22 +26082,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K382" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L382" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K382" s="5" t="n">
+        <v>8657040</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>18187</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -26514,22 +26278,18 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K385" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L385" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K385" s="5" t="n">
+        <v>7415520</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>17740</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N385" s="3" t="inlineStr">
@@ -26646,22 +26406,18 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K387" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L387" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K387" s="5" t="n">
+        <v>5617080</v>
+      </c>
+      <c r="L387" s="5" t="n">
+        <v>18356</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N387" s="3" t="inlineStr">
@@ -26846,22 +26602,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="n">
+        <v>8631000</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>18132</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -27046,22 +26798,18 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="n">
+        <v>7401240</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>17706</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N393" s="3" t="inlineStr">
@@ -27178,22 +26926,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K395" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L395" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K395" s="5" t="n">
+        <v>5600280</v>
+      </c>
+      <c r="L395" s="5" t="n">
+        <v>18302</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -27378,22 +27122,18 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K398" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L398" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K398" s="5" t="n">
+        <v>8604960</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>18078</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N398" s="3" t="inlineStr">
@@ -27578,22 +27318,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K401" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L401" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K401" s="5" t="n">
+        <v>7386120</v>
+      </c>
+      <c r="L401" s="5" t="n">
+        <v>17670</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -27710,22 +27446,18 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K403" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L403" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K403" s="5" t="n">
+        <v>5583480</v>
+      </c>
+      <c r="L403" s="5" t="n">
+        <v>18247</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N403" s="3" t="inlineStr">
@@ -28114,22 +27846,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K409" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L409" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K409" s="5" t="n">
+        <v>7386120</v>
+      </c>
+      <c r="L409" s="5" t="n">
+        <v>17670</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -28586,22 +28314,18 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>7974960</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>17801</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N416" s="3" t="inlineStr">
@@ -28650,22 +28374,18 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>7356720</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>17600</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N417" s="3" t="inlineStr">
@@ -29122,22 +28842,18 @@
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K424" s="5" t="n">
+        <v>7951440</v>
+      </c>
+      <c r="L424" s="5" t="n">
+        <v>17749</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N424" s="3" t="inlineStr">
@@ -29186,22 +28902,18 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K425" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L425" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K425" s="5" t="n">
+        <v>7342440</v>
+      </c>
+      <c r="L425" s="5" t="n">
+        <v>17566</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N425" s="3" t="inlineStr">
@@ -29522,22 +29234,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K430" s="5" t="n">
+        <v>8502480</v>
+      </c>
+      <c r="L430" s="5" t="n">
+        <v>17862</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -29654,22 +29362,18 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K432" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L432" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K432" s="5" t="n">
+        <v>7927920</v>
+      </c>
+      <c r="L432" s="5" t="n">
+        <v>17696</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N432" s="3" t="inlineStr">
@@ -29718,22 +29422,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K433" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L433" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K433" s="5" t="n">
+        <v>7327320</v>
+      </c>
+      <c r="L433" s="5" t="n">
+        <v>17529</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -29850,22 +29550,18 @@
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K435" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L435" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K435" s="5" t="n">
+        <v>5516280</v>
+      </c>
+      <c r="L435" s="5" t="n">
+        <v>18027</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N435" s="3" t="inlineStr">
@@ -30050,22 +29746,18 @@
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K438" s="5" t="n">
+        <v>8459640</v>
+      </c>
+      <c r="L438" s="5" t="n">
+        <v>17772</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N438" s="3" t="inlineStr">
@@ -30182,22 +29874,18 @@
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K440" s="5" t="n">
+        <v>7887600</v>
+      </c>
+      <c r="L440" s="5" t="n">
+        <v>17606</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N440" s="3" t="inlineStr">
@@ -30246,22 +29934,18 @@
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K441" s="5" t="n">
+        <v>7313040</v>
+      </c>
+      <c r="L441" s="5" t="n">
+        <v>17495</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N441" s="3" t="inlineStr">
@@ -30378,22 +30062,18 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K443" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L443" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K443" s="5" t="n">
+        <v>5500320</v>
+      </c>
+      <c r="L443" s="5" t="n">
+        <v>17975</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N443" s="3" t="inlineStr">
@@ -30578,22 +30258,18 @@
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K446" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L446" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K446" s="5" t="n">
+        <v>8400840</v>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>17649</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N446" s="3" t="inlineStr">
@@ -30710,22 +30386,18 @@
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K448" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L448" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K448" s="5" t="n">
+        <v>7833000</v>
+      </c>
+      <c r="L448" s="5" t="n">
+        <v>17484</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N448" s="3" t="inlineStr">
@@ -30774,22 +30446,18 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K449" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L449" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K449" s="5" t="n">
+        <v>7297920</v>
+      </c>
+      <c r="L449" s="5" t="n">
+        <v>17459</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N449" s="3" t="inlineStr">
@@ -30906,22 +30574,18 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K451" s="5" t="n">
+        <v>5483520</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>17920</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N451" s="3" t="inlineStr">
@@ -31242,22 +30906,18 @@
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K456" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L456" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K456" s="5" t="n">
+        <v>7715400</v>
+      </c>
+      <c r="L456" s="5" t="n">
+        <v>17222</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N456" s="3" t="inlineStr">
@@ -31306,22 +30966,18 @@
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K457" s="5" t="n">
+        <v>7283640</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>17425</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N457" s="3" t="inlineStr">
@@ -31778,22 +31434,18 @@
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K464" s="5" t="n">
+        <v>7522200</v>
+      </c>
+      <c r="L464" s="5" t="n">
+        <v>16791</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N464" s="3" t="inlineStr">
@@ -31842,22 +31494,18 @@
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K465" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L465" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K465" s="5" t="n">
+        <v>7268520</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>17389</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N465" s="3" t="inlineStr">
@@ -32314,22 +31962,18 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K472" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L472" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K472" s="5" t="n">
+        <v>7522200</v>
+      </c>
+      <c r="L472" s="5" t="n">
+        <v>16791</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N472" s="3" t="inlineStr">
@@ -32378,22 +32022,18 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K473" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L473" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K473" s="5" t="n">
+        <v>7268520</v>
+      </c>
+      <c r="L473" s="5" t="n">
+        <v>17389</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N473" s="3" t="inlineStr">
@@ -32714,22 +32354,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K478" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L478" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K478" s="5" t="n">
+        <v>8019480</v>
+      </c>
+      <c r="L478" s="5" t="n">
+        <v>16848</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -32846,22 +32482,18 @@
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K480" s="5" t="n">
+        <v>7476840</v>
+      </c>
+      <c r="L480" s="5" t="n">
+        <v>16689</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N480" s="3" t="inlineStr">
@@ -32910,22 +32542,18 @@
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K481" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L481" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K481" s="5" t="n">
+        <v>7239960</v>
+      </c>
+      <c r="L481" s="5" t="n">
+        <v>17320</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N481" s="3" t="inlineStr">
@@ -33042,22 +32670,18 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K483" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L483" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K483" s="5" t="n">
+        <v>5418000</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>17706</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N483" s="3" t="inlineStr">
@@ -33242,22 +32866,18 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K486" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L486" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K486" s="5" t="n">
+        <v>7995120</v>
+      </c>
+      <c r="L486" s="5" t="n">
+        <v>16796</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N486" s="3" t="inlineStr">
@@ -33374,22 +32994,18 @@
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K488" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L488" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K488" s="5" t="n">
+        <v>7455000</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>16641</v>
       </c>
       <c r="M488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N488" s="3" t="inlineStr">
@@ -33438,22 +33054,18 @@
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K489" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L489" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K489" s="5" t="n">
+        <v>7167720</v>
+      </c>
+      <c r="L489" s="5" t="n">
+        <v>17148</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N489" s="3" t="inlineStr">
@@ -33570,22 +33182,18 @@
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K491" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L491" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K491" s="5" t="n">
+        <v>5364240</v>
+      </c>
+      <c r="L491" s="5" t="n">
+        <v>17530</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N491" s="3" t="inlineStr">
@@ -33770,22 +33378,18 @@
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K494" s="5" t="n">
+        <v>7947240</v>
+      </c>
+      <c r="L494" s="5" t="n">
+        <v>16696</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N494" s="3" t="inlineStr">
@@ -33902,22 +33506,18 @@
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K496" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L496" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K496" s="5" t="n">
+        <v>7408800</v>
+      </c>
+      <c r="L496" s="5" t="n">
+        <v>16538</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N496" s="3" t="inlineStr">
@@ -33966,22 +33566,18 @@
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K497" s="5" t="n">
+        <v>6987960</v>
+      </c>
+      <c r="L497" s="5" t="n">
+        <v>16718</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N497" s="3" t="inlineStr">
@@ -34098,22 +33694,18 @@
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K499" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L499" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K499" s="5" t="n">
+        <v>5297880</v>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>17313</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N499" s="3" t="inlineStr">

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>727000</v>
+        <v>14727000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>484</v>
+        <v>22484</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>610680</v>
+        <v>12370680</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>932</v>
+        <v>18887</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>683000</v>
+        <v>14683000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>417</v>
+        <v>22417</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>573720</v>
+        <v>12333720</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>876</v>
+        <v>18830</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>639000</v>
+        <v>14639000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>350</v>
+        <v>22350</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>536760</v>
+        <v>12296760</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>819</v>
+        <v>18774</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>595000</v>
+        <v>14595000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>282</v>
+        <v>22282</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>499800</v>
+        <v>12259800</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>763</v>
+        <v>18717</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>552000</v>
+        <v>14552000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>217</v>
+        <v>22217</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>463680</v>
+        <v>12223680</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>708</v>
+        <v>18662</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>508000</v>
+        <v>14508000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>150</v>
+        <v>22150</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>426720</v>
+        <v>12186720</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>651</v>
+        <v>18606</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>465000</v>
+        <v>14465000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>84</v>
+        <v>22084</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>390600</v>
+        <v>12150600</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>596</v>
+        <v>18551</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -7094,10 +7094,10 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>465000</v>
+        <v>14465000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>84</v>
+        <v>22084</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>390600</v>
+        <v>12150600</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>596</v>
+        <v>18551</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>379000</v>
+        <v>14379000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>953</v>
+        <v>21953</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>318360</v>
+        <v>12078360</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>486</v>
+        <v>18440</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>193000</v>
+        <v>14193000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>603</v>
+        <v>21603</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="K122" s="5" t="n">
-        <v>162120</v>
+        <v>11922120</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>247</v>
+        <v>18146</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="H127" s="5" t="n">
-        <v>164000</v>
+        <v>14164000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>559</v>
+        <v>21559</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>137760</v>
+        <v>11897760</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>210</v>
+        <v>18109</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>136000</v>
+        <v>14136000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>516</v>
+        <v>21516</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>114240</v>
+        <v>11874240</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>174</v>
+        <v>18073</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>10000</v>
+        <v>9010000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>351</v>
+        <v>21351</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="K138" s="5" t="n">
-        <v>8400</v>
+        <v>7568400</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>20</v>
+        <v>17935</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>983000</v>
+        <v>8983000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>287</v>
+        <v>21287</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>825720</v>
+        <v>7545720</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>1957</v>
+        <v>17881</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>956000</v>
+        <v>8956000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>223</v>
+        <v>21223</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>803040</v>
+        <v>7523040</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>1903</v>
+        <v>17827</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10770,10 +10770,10 @@
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>23000</v>
+        <v>14023000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>344</v>
+        <v>21344</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10781,10 +10781,10 @@
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>19320</v>
+        <v>11779320</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>29</v>
+        <v>17929</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="H153" s="5" t="n">
-        <v>911000</v>
+        <v>8911000</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>116</v>
+        <v>21116</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>765240</v>
+        <v>7485240</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>1813</v>
+        <v>17738</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>995000</v>
+        <v>13995000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>301</v>
+        <v>21301</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>835800</v>
+        <v>11755800</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>1272</v>
+        <v>17893</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>849000</v>
+        <v>8849000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>969</v>
+        <v>20969</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -11165,10 +11165,10 @@
         </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>713160</v>
+        <v>7433160</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>1690</v>
+        <v>17614</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>967000</v>
+        <v>13967000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>259</v>
+        <v>21259</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11429,10 +11429,10 @@
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>812280</v>
+        <v>11732280</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>1236</v>
+        <v>17857</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>716000</v>
+        <v>8716000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>654</v>
+        <v>20654</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11489,10 +11489,10 @@
         </is>
       </c>
       <c r="K163" s="5" t="n">
-        <v>601440</v>
+        <v>7321440</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>1425</v>
+        <v>17349</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>498000</v>
+        <v>8498000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>137</v>
+        <v>20137</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11821,10 +11821,10 @@
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>418320</v>
+        <v>7138320</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>991</v>
+        <v>16915</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -12142,10 +12142,10 @@
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>498000</v>
+        <v>8498000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>137</v>
+        <v>20137</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>418320</v>
+        <v>7138320</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>991</v>
+        <v>16915</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>447000</v>
+        <v>8447000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>17</v>
+        <v>20017</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>375480</v>
+        <v>7095480</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>890</v>
+        <v>16814</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12738,10 +12738,10 @@
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>856000</v>
+        <v>13856000</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>90</v>
+        <v>21090</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -12749,10 +12749,10 @@
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>719040</v>
+        <v>11639040</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>1094</v>
+        <v>17715</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -12798,10 +12798,10 @@
         </is>
       </c>
       <c r="H183" s="5" t="n">
-        <v>422000</v>
+        <v>8422000</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>957</v>
+        <v>19957</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="K183" s="5" t="n">
-        <v>354480</v>
+        <v>7074480</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>840</v>
+        <v>16764</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -13062,10 +13062,10 @@
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>828000</v>
+        <v>13828000</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>47</v>
+        <v>21047</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -13073,10 +13073,10 @@
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>695520</v>
+        <v>11615520</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>1059</v>
+        <v>17680</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -13122,10 +13122,10 @@
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>372000</v>
+        <v>8372000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>839</v>
+        <v>19839</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -13133,10 +13133,10 @@
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>312480</v>
+        <v>7032480</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>740</v>
+        <v>16665</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>818000</v>
+        <v>13818000</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>32</v>
+        <v>21032</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>687120</v>
+        <v>11607120</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>1046</v>
+        <v>17667</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="H225" s="5" t="n">
-        <v>322000</v>
+        <v>9322000</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>301</v>
+        <v>22301</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>270480</v>
+        <v>7830480</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>647</v>
+        <v>18733</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>295000</v>
+        <v>9295000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>237</v>
+        <v>22237</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16169,10 +16169,10 @@
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>247800</v>
+        <v>7807800</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>593</v>
+        <v>18679</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -16694,10 +16694,10 @@
         </is>
       </c>
       <c r="H241" s="5" t="n">
-        <v>267000</v>
+        <v>9267000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>170</v>
+        <v>22170</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16705,10 +16705,10 @@
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>224280</v>
+        <v>7784280</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>537</v>
+        <v>18623</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -17230,10 +17230,10 @@
         </is>
       </c>
       <c r="H249" s="5" t="n">
-        <v>239000</v>
+        <v>9239000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>103</v>
+        <v>22103</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -17241,10 +17241,10 @@
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>200760</v>
+        <v>7760760</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>480</v>
+        <v>18566</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -17766,10 +17766,10 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>211000</v>
+        <v>9211000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>36</v>
+        <v>22036</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -17777,10 +17777,10 @@
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>177240</v>
+        <v>7737240</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>424</v>
+        <v>18510</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -18302,10 +18302,10 @@
         </is>
       </c>
       <c r="H265" s="5" t="n">
-        <v>184000</v>
+        <v>9184000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>971</v>
+        <v>21971</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -18313,10 +18313,10 @@
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>154560</v>
+        <v>7714560</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>370</v>
+        <v>18456</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -18838,10 +18838,10 @@
         </is>
       </c>
       <c r="H273" s="5" t="n">
-        <v>184000</v>
+        <v>9184000</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>971</v>
+        <v>21971</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>154560</v>
+        <v>7714560</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>370</v>
+        <v>18456</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>129000</v>
+        <v>9129000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>840</v>
+        <v>21840</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -19385,10 +19385,10 @@
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>108360</v>
+        <v>7668360</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>259</v>
+        <v>18345</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -19910,10 +19910,10 @@
         </is>
       </c>
       <c r="H289" s="5" t="n">
-        <v>102000</v>
+        <v>9102000</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>775</v>
+        <v>21775</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -19921,10 +19921,10 @@
         </is>
       </c>
       <c r="K289" s="5" t="n">
-        <v>85680</v>
+        <v>7645680</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>205</v>
+        <v>18291</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -20038,10 +20038,10 @@
         </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>27000</v>
+        <v>7027000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>964</v>
+        <v>22964</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -20049,10 +20049,10 @@
         </is>
       </c>
       <c r="K291" s="5" t="n">
-        <v>22680</v>
+        <v>5902680</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>74</v>
+        <v>19290</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -20438,10 +20438,10 @@
         </is>
       </c>
       <c r="H297" s="5" t="n">
-        <v>75000</v>
+        <v>9075000</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>711</v>
+        <v>21711</v>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="K297" s="5" t="n">
-        <v>63000</v>
+        <v>7623000</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>151</v>
+        <v>18237</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
@@ -20566,10 +20566,10 @@
         </is>
       </c>
       <c r="H299" s="5" t="n">
-        <v>6000</v>
+        <v>7006000</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>895</v>
+        <v>22895</v>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
@@ -20577,10 +20577,10 @@
         </is>
       </c>
       <c r="K299" s="5" t="n">
-        <v>5040</v>
+        <v>5885040</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>16</v>
+        <v>19232</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
@@ -20966,10 +20966,10 @@
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>47000</v>
+        <v>9047000</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>644</v>
+        <v>21644</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
@@ -20977,10 +20977,10 @@
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>39480</v>
+        <v>7599480</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>94</v>
+        <v>18181</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
@@ -21094,10 +21094,10 @@
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>985000</v>
+        <v>6985000</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>827</v>
+        <v>22827</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -21105,10 +21105,10 @@
         </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>827400</v>
+        <v>5867400</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>2704</v>
+        <v>19175</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -21494,10 +21494,10 @@
         </is>
       </c>
       <c r="H313" s="5" t="n">
-        <v>20000</v>
+        <v>9020000</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>579</v>
+        <v>21579</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
@@ -21505,10 +21505,10 @@
         </is>
       </c>
       <c r="K313" s="5" t="n">
-        <v>16800</v>
+        <v>7576800</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>40</v>
+        <v>18126</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -21622,10 +21622,10 @@
         </is>
       </c>
       <c r="H315" s="5" t="n">
-        <v>964000</v>
+        <v>6964000</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>758</v>
+        <v>22758</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
@@ -21633,10 +21633,10 @@
         </is>
       </c>
       <c r="K315" s="5" t="n">
-        <v>809760</v>
+        <v>5849760</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>2646</v>
+        <v>19117</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -22022,10 +22022,10 @@
         </is>
       </c>
       <c r="H321" s="5" t="n">
-        <v>993000</v>
+        <v>8993000</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>514</v>
+        <v>21514</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -22033,10 +22033,10 @@
         </is>
       </c>
       <c r="K321" s="5" t="n">
-        <v>834120</v>
+        <v>7554120</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>1996</v>
+        <v>18072</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="H323" s="5" t="n">
-        <v>943000</v>
+        <v>6943000</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>690</v>
+        <v>22690</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
@@ -22161,10 +22161,10 @@
         </is>
       </c>
       <c r="K323" s="5" t="n">
-        <v>792120</v>
+        <v>5832120</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>2589</v>
+        <v>19059</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -22550,10 +22550,10 @@
         </is>
       </c>
       <c r="H329" s="5" t="n">
-        <v>966000</v>
+        <v>8966000</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>450</v>
+        <v>21450</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -22561,10 +22561,10 @@
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>811440</v>
+        <v>7531440</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>1941</v>
+        <v>18018</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
@@ -22678,10 +22678,10 @@
         </is>
       </c>
       <c r="H331" s="5" t="n">
-        <v>922000</v>
+        <v>6922000</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>621</v>
+        <v>22621</v>
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
@@ -22689,10 +22689,10 @@
         </is>
       </c>
       <c r="K331" s="5" t="n">
-        <v>774480</v>
+        <v>5814480</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>2531</v>
+        <v>19002</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
@@ -23078,10 +23078,10 @@
         </is>
       </c>
       <c r="H337" s="5" t="n">
-        <v>940000</v>
+        <v>8940000</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>388</v>
+        <v>21388</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
@@ -23089,10 +23089,10 @@
         </is>
       </c>
       <c r="K337" s="5" t="n">
-        <v>789600</v>
+        <v>7509600</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>1889</v>
+        <v>17966</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -23206,10 +23206,10 @@
         </is>
       </c>
       <c r="H339" s="5" t="n">
-        <v>902000</v>
+        <v>6902000</v>
       </c>
       <c r="I339" s="5" t="n">
-        <v>556</v>
+        <v>22556</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
@@ -23217,10 +23217,10 @@
         </is>
       </c>
       <c r="K339" s="5" t="n">
-        <v>757680</v>
+        <v>5797680</v>
       </c>
       <c r="L339" s="5" t="n">
-        <v>2476</v>
+        <v>18947</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
@@ -23606,10 +23606,10 @@
         </is>
       </c>
       <c r="H345" s="5" t="n">
-        <v>940000</v>
+        <v>8940000</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>388</v>
+        <v>21388</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -23617,10 +23617,10 @@
         </is>
       </c>
       <c r="K345" s="5" t="n">
-        <v>789600</v>
+        <v>7509600</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>1889</v>
+        <v>17966</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="H347" s="5" t="n">
-        <v>902000</v>
+        <v>6902000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>556</v>
+        <v>22556</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -23745,10 +23745,10 @@
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>757680</v>
+        <v>5797680</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>2476</v>
+        <v>18947</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -24134,10 +24134,10 @@
         </is>
       </c>
       <c r="H353" s="5" t="n">
-        <v>886000</v>
+        <v>8886000</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>258</v>
+        <v>21258</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
@@ -24145,10 +24145,10 @@
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>744240</v>
+        <v>7464240</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>1780</v>
+        <v>17857</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -24262,10 +24262,10 @@
         </is>
       </c>
       <c r="H355" s="5" t="n">
-        <v>861000</v>
+        <v>6861000</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>422</v>
+        <v>22422</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
@@ -24273,10 +24273,10 @@
         </is>
       </c>
       <c r="K355" s="5" t="n">
-        <v>723240</v>
+        <v>5763240</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>2364</v>
+        <v>18834</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
@@ -24662,10 +24662,10 @@
         </is>
       </c>
       <c r="H361" s="5" t="n">
-        <v>882000</v>
+        <v>8882000</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>47</v>
+        <v>21047</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -24673,10 +24673,10 @@
         </is>
       </c>
       <c r="K361" s="5" t="n">
-        <v>740880</v>
+        <v>7460880</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>1756</v>
+        <v>17680</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
@@ -25198,10 +25198,10 @@
         </is>
       </c>
       <c r="H369" s="5" t="n">
-        <v>864000</v>
+        <v>8864000</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>5</v>
+        <v>21005</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -25209,10 +25209,10 @@
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>725760</v>
+        <v>7445760</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>1720</v>
+        <v>17644</v>
       </c>
       <c r="M369" s="3" t="inlineStr">
         <is>
@@ -25734,10 +25734,10 @@
         </is>
       </c>
       <c r="H377" s="5" t="n">
-        <v>846000</v>
+        <v>8846000</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>962</v>
+        <v>20962</v>
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
@@ -25745,10 +25745,10 @@
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>710640</v>
+        <v>7430640</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>1684</v>
+        <v>17608</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
@@ -26066,10 +26066,10 @@
         </is>
       </c>
       <c r="H382" s="5" t="n">
-        <v>306000</v>
+        <v>10306000</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>651</v>
+        <v>21651</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -26077,10 +26077,10 @@
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>257040</v>
+        <v>8657040</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>540</v>
+        <v>18187</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -26262,10 +26262,10 @@
         </is>
       </c>
       <c r="H385" s="5" t="n">
-        <v>828000</v>
+        <v>8828000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>919</v>
+        <v>20919</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -26273,10 +26273,10 @@
         </is>
       </c>
       <c r="K385" s="5" t="n">
-        <v>695520</v>
+        <v>7415520</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>1648</v>
+        <v>17572</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
@@ -26390,10 +26390,10 @@
         </is>
       </c>
       <c r="H387" s="5" t="n">
-        <v>687000</v>
+        <v>6687000</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>997</v>
+        <v>21997</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -26401,10 +26401,10 @@
         </is>
       </c>
       <c r="K387" s="5" t="n">
-        <v>577080</v>
+        <v>5617080</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>1898</v>
+        <v>18477</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
@@ -26586,10 +26586,10 @@
         </is>
       </c>
       <c r="H390" s="5" t="n">
-        <v>275000</v>
+        <v>10275000</v>
       </c>
       <c r="I390" s="5" t="n">
-        <v>586</v>
+        <v>21586</v>
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
@@ -26597,10 +26597,10 @@
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>231000</v>
+        <v>8631000</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>485</v>
+        <v>18132</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
@@ -26782,10 +26782,10 @@
         </is>
       </c>
       <c r="H393" s="5" t="n">
-        <v>811000</v>
+        <v>8811000</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>879</v>
+        <v>20879</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -26793,10 +26793,10 @@
         </is>
       </c>
       <c r="K393" s="5" t="n">
-        <v>681240</v>
+        <v>7401240</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>1614</v>
+        <v>17538</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -26910,10 +26910,10 @@
         </is>
       </c>
       <c r="H395" s="5" t="n">
-        <v>667000</v>
+        <v>6667000</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>931</v>
+        <v>21931</v>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
@@ -26921,10 +26921,10 @@
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>560280</v>
+        <v>5600280</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>1843</v>
+        <v>18422</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -27106,10 +27106,10 @@
         </is>
       </c>
       <c r="H398" s="5" t="n">
-        <v>244000</v>
+        <v>10244000</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>521</v>
+        <v>21521</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
@@ -27117,10 +27117,10 @@
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>204960</v>
+        <v>8604960</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>431</v>
+        <v>18078</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
@@ -27302,10 +27302,10 @@
         </is>
       </c>
       <c r="H401" s="5" t="n">
-        <v>793000</v>
+        <v>8793000</v>
       </c>
       <c r="I401" s="5" t="n">
-        <v>836</v>
+        <v>20836</v>
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
@@ -27313,10 +27313,10 @@
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>666120</v>
+        <v>7386120</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>1578</v>
+        <v>17503</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
@@ -27430,10 +27430,10 @@
         </is>
       </c>
       <c r="H403" s="5" t="n">
-        <v>647000</v>
+        <v>6647000</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>865</v>
+        <v>21865</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
@@ -27441,10 +27441,10 @@
         </is>
       </c>
       <c r="K403" s="5" t="n">
-        <v>543480</v>
+        <v>5583480</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>1788</v>
+        <v>18367</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -27830,10 +27830,10 @@
         </is>
       </c>
       <c r="H409" s="5" t="n">
-        <v>793000</v>
+        <v>8793000</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>836</v>
+        <v>20836</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -27841,10 +27841,10 @@
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>666120</v>
+        <v>7386120</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>1578</v>
+        <v>17503</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -28298,10 +28298,10 @@
         </is>
       </c>
       <c r="H416" s="5" t="n">
-        <v>494000</v>
+        <v>9494000</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>192</v>
+        <v>21192</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -28309,10 +28309,10 @@
         </is>
       </c>
       <c r="K416" s="5" t="n">
-        <v>414960</v>
+        <v>7974960</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>926</v>
+        <v>17801</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -28358,10 +28358,10 @@
         </is>
       </c>
       <c r="H417" s="5" t="n">
-        <v>758000</v>
+        <v>8758000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>754</v>
+        <v>20754</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -28369,10 +28369,10 @@
         </is>
       </c>
       <c r="K417" s="5" t="n">
-        <v>636720</v>
+        <v>7356720</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>1509</v>
+        <v>17433</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -28826,10 +28826,10 @@
         </is>
       </c>
       <c r="H424" s="5" t="n">
-        <v>466000</v>
+        <v>9466000</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>129</v>
+        <v>21129</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
@@ -28837,10 +28837,10 @@
         </is>
       </c>
       <c r="K424" s="5" t="n">
-        <v>391440</v>
+        <v>7951440</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>874</v>
+        <v>17749</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
@@ -28886,10 +28886,10 @@
         </is>
       </c>
       <c r="H425" s="5" t="n">
-        <v>741000</v>
+        <v>8741000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>713</v>
+        <v>20713</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -28897,10 +28897,10 @@
         </is>
       </c>
       <c r="K425" s="5" t="n">
-        <v>622440</v>
+        <v>7342440</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>1475</v>
+        <v>17399</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -29218,10 +29218,10 @@
         </is>
       </c>
       <c r="H430" s="5" t="n">
-        <v>122000</v>
+        <v>10122000</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>265</v>
+        <v>21265</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
@@ -29229,10 +29229,10 @@
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>102480</v>
+        <v>8502480</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>215</v>
+        <v>17862</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
@@ -29346,10 +29346,10 @@
         </is>
       </c>
       <c r="H432" s="5" t="n">
-        <v>438000</v>
+        <v>9438000</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>67</v>
+        <v>21067</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
@@ -29357,10 +29357,10 @@
         </is>
       </c>
       <c r="K432" s="5" t="n">
-        <v>367920</v>
+        <v>7927920</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>821</v>
+        <v>17696</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -29406,10 +29406,10 @@
         </is>
       </c>
       <c r="H433" s="5" t="n">
-        <v>723000</v>
+        <v>8723000</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>671</v>
+        <v>20671</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
@@ -29417,10 +29417,10 @@
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>607320</v>
+        <v>7327320</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>1439</v>
+        <v>17363</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -29534,10 +29534,10 @@
         </is>
       </c>
       <c r="H435" s="5" t="n">
-        <v>567000</v>
+        <v>6567000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>602</v>
+        <v>21602</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -29545,10 +29545,10 @@
         </is>
       </c>
       <c r="K435" s="5" t="n">
-        <v>476280</v>
+        <v>5516280</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>1567</v>
+        <v>18146</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -29730,10 +29730,10 @@
         </is>
       </c>
       <c r="H438" s="5" t="n">
-        <v>71000</v>
+        <v>10071000</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>158</v>
+        <v>21158</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
@@ -29741,10 +29741,10 @@
         </is>
       </c>
       <c r="K438" s="5" t="n">
-        <v>59640</v>
+        <v>8459640</v>
       </c>
       <c r="L438" s="5" t="n">
-        <v>125</v>
+        <v>17772</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
@@ -29858,10 +29858,10 @@
         </is>
       </c>
       <c r="H440" s="5" t="n">
-        <v>390000</v>
+        <v>9390000</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>960</v>
+        <v>20960</v>
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
@@ -29869,10 +29869,10 @@
         </is>
       </c>
       <c r="K440" s="5" t="n">
-        <v>327600</v>
+        <v>7887600</v>
       </c>
       <c r="L440" s="5" t="n">
-        <v>731</v>
+        <v>17606</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
@@ -29918,10 +29918,10 @@
         </is>
       </c>
       <c r="H441" s="5" t="n">
-        <v>706000</v>
+        <v>8706000</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>630</v>
+        <v>20630</v>
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
@@ -29929,10 +29929,10 @@
         </is>
       </c>
       <c r="K441" s="5" t="n">
-        <v>593040</v>
+        <v>7313040</v>
       </c>
       <c r="L441" s="5" t="n">
-        <v>1405</v>
+        <v>17329</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
@@ -30046,10 +30046,10 @@
         </is>
       </c>
       <c r="H443" s="5" t="n">
-        <v>548000</v>
+        <v>6548000</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>539</v>
+        <v>21539</v>
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
@@ -30057,10 +30057,10 @@
         </is>
       </c>
       <c r="K443" s="5" t="n">
-        <v>460320</v>
+        <v>5500320</v>
       </c>
       <c r="L443" s="5" t="n">
-        <v>1514</v>
+        <v>18093</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
@@ -30242,10 +30242,10 @@
         </is>
       </c>
       <c r="H446" s="5" t="n">
-        <v>1000</v>
+        <v>10001000</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>11</v>
+        <v>21011</v>
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
@@ -30253,10 +30253,10 @@
         </is>
       </c>
       <c r="K446" s="5" t="n">
-        <v>840</v>
+        <v>8400840</v>
       </c>
       <c r="L446" s="5" t="n">
-        <v>2</v>
+        <v>17649</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
@@ -30370,10 +30370,10 @@
         </is>
       </c>
       <c r="H448" s="5" t="n">
-        <v>325000</v>
+        <v>9325000</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>815</v>
+        <v>20815</v>
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
@@ -30381,10 +30381,10 @@
         </is>
       </c>
       <c r="K448" s="5" t="n">
-        <v>273000</v>
+        <v>7833000</v>
       </c>
       <c r="L448" s="5" t="n">
-        <v>609</v>
+        <v>17484</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         </is>
       </c>
       <c r="H449" s="5" t="n">
-        <v>688000</v>
+        <v>8688000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>588</v>
+        <v>20588</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -30441,10 +30441,10 @@
         </is>
       </c>
       <c r="K449" s="5" t="n">
-        <v>577920</v>
+        <v>7297920</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>1369</v>
+        <v>17294</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -30558,10 +30558,10 @@
         </is>
       </c>
       <c r="H451" s="5" t="n">
-        <v>528000</v>
+        <v>6528000</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>474</v>
+        <v>21474</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -30569,10 +30569,10 @@
         </is>
       </c>
       <c r="K451" s="5" t="n">
-        <v>443520</v>
+        <v>5483520</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>1459</v>
+        <v>18038</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -30890,10 +30890,10 @@
         </is>
       </c>
       <c r="H456" s="5" t="n">
-        <v>185000</v>
+        <v>9185000</v>
       </c>
       <c r="I456" s="5" t="n">
-        <v>502</v>
+        <v>20502</v>
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
@@ -30901,10 +30901,10 @@
         </is>
       </c>
       <c r="K456" s="5" t="n">
-        <v>155400</v>
+        <v>7715400</v>
       </c>
       <c r="L456" s="5" t="n">
-        <v>347</v>
+        <v>17222</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
@@ -30950,10 +30950,10 @@
         </is>
       </c>
       <c r="H457" s="5" t="n">
-        <v>671000</v>
+        <v>8671000</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>547</v>
+        <v>20547</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
@@ -30961,10 +30961,10 @@
         </is>
       </c>
       <c r="K457" s="5" t="n">
-        <v>563640</v>
+        <v>7283640</v>
       </c>
       <c r="L457" s="5" t="n">
-        <v>1336</v>
+        <v>17260</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -31418,10 +31418,10 @@
         </is>
       </c>
       <c r="H464" s="5" t="n">
-        <v>955000</v>
+        <v>8955000</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>989</v>
+        <v>19989</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
@@ -31429,10 +31429,10 @@
         </is>
       </c>
       <c r="K464" s="5" t="n">
-        <v>802200</v>
+        <v>7522200</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>1791</v>
+        <v>16791</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
@@ -31478,10 +31478,10 @@
         </is>
       </c>
       <c r="H465" s="5" t="n">
-        <v>653000</v>
+        <v>8653000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>505</v>
+        <v>20505</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -31489,10 +31489,10 @@
         </is>
       </c>
       <c r="K465" s="5" t="n">
-        <v>548520</v>
+        <v>7268520</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>1300</v>
+        <v>17224</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="H472" s="5" t="n">
-        <v>955000</v>
+        <v>8955000</v>
       </c>
       <c r="I472" s="5" t="n">
-        <v>989</v>
+        <v>19989</v>
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
@@ -31957,10 +31957,10 @@
         </is>
       </c>
       <c r="K472" s="5" t="n">
-        <v>802200</v>
+        <v>7522200</v>
       </c>
       <c r="L472" s="5" t="n">
-        <v>1791</v>
+        <v>16791</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
@@ -32006,10 +32006,10 @@
         </is>
       </c>
       <c r="H473" s="5" t="n">
-        <v>653000</v>
+        <v>8653000</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>505</v>
+        <v>20505</v>
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
@@ -32017,10 +32017,10 @@
         </is>
       </c>
       <c r="K473" s="5" t="n">
-        <v>548520</v>
+        <v>7268520</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>1300</v>
+        <v>17224</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
@@ -32338,10 +32338,10 @@
         </is>
       </c>
       <c r="H478" s="5" t="n">
-        <v>547000</v>
+        <v>9547000</v>
       </c>
       <c r="I478" s="5" t="n">
-        <v>57</v>
+        <v>20057</v>
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
@@ -32349,10 +32349,10 @@
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>459480</v>
+        <v>8019480</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>965</v>
+        <v>16848</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -32466,10 +32466,10 @@
         </is>
       </c>
       <c r="H480" s="5" t="n">
-        <v>901000</v>
+        <v>8901000</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>868</v>
+        <v>19868</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -32477,10 +32477,10 @@
         </is>
       </c>
       <c r="K480" s="5" t="n">
-        <v>756840</v>
+        <v>7476840</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>1689</v>
+        <v>16689</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -32526,10 +32526,10 @@
         </is>
       </c>
       <c r="H481" s="5" t="n">
-        <v>619000</v>
+        <v>8619000</v>
       </c>
       <c r="I481" s="5" t="n">
-        <v>424</v>
+        <v>20424</v>
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
@@ -32537,10 +32537,10 @@
         </is>
       </c>
       <c r="K481" s="5" t="n">
-        <v>519960</v>
+        <v>7239960</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>1232</v>
+        <v>17156</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
@@ -32654,10 +32654,10 @@
         </is>
       </c>
       <c r="H483" s="5" t="n">
-        <v>450000</v>
+        <v>6450000</v>
       </c>
       <c r="I483" s="5" t="n">
-        <v>217</v>
+        <v>21217</v>
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
@@ -32665,10 +32665,10 @@
         </is>
       </c>
       <c r="K483" s="5" t="n">
-        <v>378000</v>
+        <v>5418000</v>
       </c>
       <c r="L483" s="5" t="n">
-        <v>1243</v>
+        <v>17822</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
@@ -32850,10 +32850,10 @@
         </is>
       </c>
       <c r="H486" s="5" t="n">
-        <v>518000</v>
+        <v>9518000</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>996</v>
+        <v>19996</v>
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
@@ -32861,10 +32861,10 @@
         </is>
       </c>
       <c r="K486" s="5" t="n">
-        <v>435120</v>
+        <v>7995120</v>
       </c>
       <c r="L486" s="5" t="n">
-        <v>914</v>
+        <v>16796</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
@@ -32978,10 +32978,10 @@
         </is>
       </c>
       <c r="H488" s="5" t="n">
-        <v>875000</v>
+        <v>8875000</v>
       </c>
       <c r="I488" s="5" t="n">
-        <v>810</v>
+        <v>19810</v>
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
@@ -32989,10 +32989,10 @@
         </is>
       </c>
       <c r="K488" s="5" t="n">
-        <v>735000</v>
+        <v>7455000</v>
       </c>
       <c r="L488" s="5" t="n">
-        <v>1641</v>
+        <v>16641</v>
       </c>
       <c r="M488" s="3" t="inlineStr">
         <is>
@@ -33038,10 +33038,10 @@
         </is>
       </c>
       <c r="H489" s="5" t="n">
-        <v>533000</v>
+        <v>8533000</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>220</v>
+        <v>20220</v>
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
@@ -33049,10 +33049,10 @@
         </is>
       </c>
       <c r="K489" s="5" t="n">
-        <v>447720</v>
+        <v>7167720</v>
       </c>
       <c r="L489" s="5" t="n">
-        <v>1061</v>
+        <v>16985</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
@@ -33166,10 +33166,10 @@
         </is>
       </c>
       <c r="H491" s="5" t="n">
-        <v>386000</v>
+        <v>6386000</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>7</v>
+        <v>21007</v>
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
@@ -33177,10 +33177,10 @@
         </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>324240</v>
+        <v>5364240</v>
       </c>
       <c r="L491" s="5" t="n">
-        <v>1067</v>
+        <v>17646</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -33362,10 +33362,10 @@
         </is>
       </c>
       <c r="H494" s="5" t="n">
-        <v>461000</v>
+        <v>9461000</v>
       </c>
       <c r="I494" s="5" t="n">
-        <v>876</v>
+        <v>19876</v>
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
@@ -33373,10 +33373,10 @@
         </is>
       </c>
       <c r="K494" s="5" t="n">
-        <v>387240</v>
+        <v>7947240</v>
       </c>
       <c r="L494" s="5" t="n">
-        <v>814</v>
+        <v>16696</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
@@ -33490,10 +33490,10 @@
         </is>
       </c>
       <c r="H496" s="5" t="n">
-        <v>820000</v>
+        <v>8820000</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>688</v>
+        <v>19688</v>
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
@@ -33501,10 +33501,10 @@
         </is>
       </c>
       <c r="K496" s="5" t="n">
-        <v>688800</v>
+        <v>7408800</v>
       </c>
       <c r="L496" s="5" t="n">
-        <v>1538</v>
+        <v>16538</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
@@ -33550,10 +33550,10 @@
         </is>
       </c>
       <c r="H497" s="5" t="n">
-        <v>319000</v>
+        <v>8319000</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>713</v>
+        <v>19713</v>
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
@@ -33561,10 +33561,10 @@
         </is>
       </c>
       <c r="K497" s="5" t="n">
-        <v>267960</v>
+        <v>6987960</v>
       </c>
       <c r="L497" s="5" t="n">
-        <v>635</v>
+        <v>16559</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
@@ -33678,10 +33678,10 @@
         </is>
       </c>
       <c r="H499" s="5" t="n">
-        <v>307000</v>
+        <v>6307000</v>
       </c>
       <c r="I499" s="5" t="n">
-        <v>747</v>
+        <v>20747</v>
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
@@ -33689,10 +33689,10 @@
         </is>
       </c>
       <c r="K499" s="5" t="n">
-        <v>257880</v>
+        <v>5297880</v>
       </c>
       <c r="L499" s="5" t="n">
-        <v>848</v>
+        <v>17427</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
@@ -35016,8 +35016,8 @@
       <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$73万
-$484/呎
+$1473万
+$22,484/呎
 (在售)</t>
         </is>
       </c>
@@ -35061,8 +35061,8 @@
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$68万
-$417/呎
+$1468万
+$22,417/呎
 (在售)</t>
         </is>
       </c>
@@ -35106,8 +35106,8 @@
       <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$64万
-$350/呎
+$1464万
+$22,350/呎
 (在售)</t>
         </is>
       </c>
@@ -35151,8 +35151,8 @@
       <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$60万
-$282/呎
+$1460万
+$22,282/呎
 (在售)</t>
         </is>
       </c>
@@ -35196,8 +35196,8 @@
       <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$55万
-$217/呎
+$1455万
+$22,217/呎
 (在售)</t>
         </is>
       </c>
@@ -35241,8 +35241,8 @@
       <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$51万
-$150/呎
+$1451万
+$22,150/呎
 (在售)</t>
         </is>
       </c>
@@ -35286,8 +35286,8 @@
       <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$46万
-$84/呎
+$1446万
+$22,084/呎
 (在售)</t>
         </is>
       </c>
@@ -35331,8 +35331,8 @@
       <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$46万
-$84/呎
+$1446万
+$22,084/呎
 (在售)</t>
         </is>
       </c>
@@ -35376,8 +35376,8 @@
       <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房1套)
-$38万
-$953/呎
+$1438万
+$21,953/呎
 (在售)</t>
         </is>
       </c>
@@ -35556,8 +35556,8 @@
       <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$19万
-$603/呎
+$1419万
+$21,603/呎
 (在售)</t>
         </is>
       </c>
@@ -35601,8 +35601,8 @@
       <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$16万
-$559/呎
+$1416万
+$21,559/呎
 (在售)</t>
         </is>
       </c>
@@ -35646,8 +35646,8 @@
       <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$14万
-$516/呎
+$1414万
+$21,516/呎
 (在售)</t>
         </is>
       </c>
@@ -35768,8 +35768,8 @@
       <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$1万
-$351/呎
+$901万
+$21,351/呎
 (在售)</t>
         </is>
       </c>
@@ -35813,8 +35813,8 @@
       <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$98万
-$287/呎
+$898万
+$21,287/呎
 (在售)</t>
         </is>
       </c>
@@ -35826,8 +35826,8 @@
       <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$2万
-$344/呎
+$1402万
+$21,344/呎
 (在售)</t>
         </is>
       </c>
@@ -35858,8 +35858,8 @@
       <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$96万
-$223/呎
+$896万
+$21,223/呎
 (在售)</t>
         </is>
       </c>
@@ -35871,8 +35871,8 @@
       <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$100万
-$301/呎
+$1400万
+$21,301/呎
 (在售)</t>
         </is>
       </c>
@@ -35903,8 +35903,8 @@
       <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$91万
-$116/呎
+$891万
+$21,116/呎
 (在售)</t>
         </is>
       </c>
@@ -35916,8 +35916,8 @@
       <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$97万
-$259/呎
+$1397万
+$21,259/呎
 (在售)</t>
         </is>
       </c>
@@ -35948,8 +35948,8 @@
       <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$85万
-$969/呎
+$885万
+$20,969/呎
 (在售)</t>
         </is>
       </c>
@@ -35993,8 +35993,8 @@
       <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$72万
-$654/呎
+$872万
+$20,654/呎
 (在售)</t>
         </is>
       </c>
@@ -36038,8 +36038,8 @@
       <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$50万
-$137/呎
+$850万
+$20,137/呎
 (在售)</t>
         </is>
       </c>
@@ -36083,8 +36083,8 @@
       <c r="F39" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$50万
-$137/呎
+$850万
+$20,137/呎
 (在售)</t>
         </is>
       </c>
@@ -36096,8 +36096,8 @@
       <c r="B40" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$86万
-$90/呎
+$1386万
+$21,090/呎
 (在售)</t>
         </is>
       </c>
@@ -36128,8 +36128,8 @@
       <c r="F40" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$45万
-$17/呎
+$845万
+$20,017/呎
 (在售)</t>
         </is>
       </c>
@@ -36141,8 +36141,8 @@
       <c r="B41" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$83万
-$47/呎
+$1383万
+$21,047/呎
 (在售)</t>
         </is>
       </c>
@@ -36173,8 +36173,8 @@
       <c r="F41" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$42万
-$957/呎
+$842万
+$19,957/呎
 (在售)</t>
         </is>
       </c>
@@ -36186,8 +36186,8 @@
       <c r="B42" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房1套)
-$82万
-$32/呎
+$1382万
+$21,032/呎
 (在售)</t>
         </is>
       </c>
@@ -36218,8 +36218,8 @@
       <c r="F42" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$37万
-$839/呎
+$837万
+$19,839/呎
 (在售)</t>
         </is>
       </c>
@@ -36662,8 +36662,8 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$32万
-$301/呎
+$932万
+$22,301/呎
 (在售)</t>
         </is>
       </c>
@@ -36731,8 +36731,8 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$30万
-$237/呎
+$930万
+$22,237/呎
 (在售)</t>
         </is>
       </c>
@@ -36800,8 +36800,8 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$27万
-$170/呎
+$927万
+$22,170/呎
 (在售)</t>
         </is>
       </c>
@@ -36869,8 +36869,8 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$24万
-$103/呎
+$924万
+$22,103/呎
 (在售)</t>
         </is>
       </c>
@@ -36938,8 +36938,8 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$21万
-$36/呎
+$921万
+$22,036/呎
 (在售)</t>
         </is>
       </c>
@@ -37007,8 +37007,8 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$18万
-$971/呎
+$918万
+$21,971/呎
 (在售)</t>
         </is>
       </c>
@@ -37076,8 +37076,8 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$18万
-$971/呎
+$918万
+$21,971/呎
 (在售)</t>
         </is>
       </c>
@@ -37145,8 +37145,8 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$13万
-$840/呎
+$913万
+$21,840/呎
 (在售)</t>
         </is>
       </c>
@@ -37198,8 +37198,8 @@
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$3万
-$964/呎
+$703万
+$22,964/呎
 (在售)</t>
         </is>
       </c>
@@ -37214,8 +37214,8 @@
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$10万
-$775/呎
+$910万
+$21,775/呎
 (在售)</t>
         </is>
       </c>
@@ -37267,8 +37267,8 @@
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$1万
-$895/呎
+$701万
+$22,895/呎
 (在售)</t>
         </is>
       </c>
@@ -37283,8 +37283,8 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$8万
-$711/呎
+$908万
+$21,711/呎
 (在售)</t>
         </is>
       </c>
@@ -37336,8 +37336,8 @@
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$98万
-$827/呎
+$698万
+$22,827/呎
 (在售)</t>
         </is>
       </c>
@@ -37352,8 +37352,8 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$5万
-$644/呎
+$905万
+$21,644/呎
 (在售)</t>
         </is>
       </c>
@@ -37405,8 +37405,8 @@
       <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$96万
-$758/呎
+$696万
+$22,758/呎
 (在售)</t>
         </is>
       </c>
@@ -37421,8 +37421,8 @@
       <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$2万
-$579/呎
+$902万
+$21,579/呎
 (在售)</t>
         </is>
       </c>
@@ -37474,8 +37474,8 @@
       <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$94万
-$690/呎
+$694万
+$22,690/呎
 (在售)</t>
         </is>
       </c>
@@ -37490,8 +37490,8 @@
       <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$99万
-$514/呎
+$899万
+$21,514/呎
 (在售)</t>
         </is>
       </c>
@@ -37543,8 +37543,8 @@
       <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$92万
-$621/呎
+$692万
+$22,621/呎
 (在售)</t>
         </is>
       </c>
@@ -37559,8 +37559,8 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$97万
-$450/呎
+$897万
+$21,450/呎
 (在售)</t>
         </is>
       </c>
@@ -37612,8 +37612,8 @@
       <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$90万
-$556/呎
+$690万
+$22,556/呎
 (在售)</t>
         </is>
       </c>
@@ -37628,8 +37628,8 @@
       <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$94万
-$388/呎
+$894万
+$21,388/呎
 (在售)</t>
         </is>
       </c>
@@ -37681,8 +37681,8 @@
       <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$90万
-$556/呎
+$690万
+$22,556/呎
 (在售)</t>
         </is>
       </c>
@@ -37697,8 +37697,8 @@
       <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$94万
-$388/呎
+$894万
+$21,388/呎
 (在售)</t>
         </is>
       </c>
@@ -37750,8 +37750,8 @@
       <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$86万
-$422/呎
+$686万
+$22,422/呎
 (在售)</t>
         </is>
       </c>
@@ -37766,8 +37766,8 @@
       <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
-$89万
-$258/呎
+$889万
+$21,258/呎
 (在售)</t>
         </is>
       </c>
@@ -37835,8 +37835,8 @@
       <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$88万
-$47/呎
+$888万
+$21,047/呎
 (在售)</t>
         </is>
       </c>
@@ -37904,8 +37904,8 @@
       <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$86万
-$5/呎
+$886万
+$21,005/呎
 (在售)</t>
         </is>
       </c>
@@ -37973,8 +37973,8 @@
       <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$85万
-$962/呎
+$885万
+$20,962/呎
 (在售)</t>
         </is>
       </c>
@@ -38026,8 +38026,8 @@
       <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$69万
-$997/呎
+$669万
+$21,997/呎
 (在售)</t>
         </is>
       </c>
@@ -38042,8 +38042,8 @@
       <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$83万
-$919/呎
+$883万
+$20,919/呎
 (在售)</t>
         </is>
       </c>
@@ -38066,8 +38066,8 @@
       <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$31万
-$651/呎
+$1031万
+$21,651/呎
 (在售)</t>
         </is>
       </c>
@@ -38095,8 +38095,8 @@
       <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$67万
-$931/呎
+$667万
+$21,931/呎
 (在售)</t>
         </is>
       </c>
@@ -38111,8 +38111,8 @@
       <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$81万
-$879/呎
+$881万
+$20,879/呎
 (在售)</t>
         </is>
       </c>
@@ -38135,8 +38135,8 @@
       <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$28万
-$586/呎
+$1028万
+$21,586/呎
 (在售)</t>
         </is>
       </c>
@@ -38164,8 +38164,8 @@
       <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$65万
-$865/呎
+$665万
+$21,865/呎
 (在售)</t>
         </is>
       </c>
@@ -38180,8 +38180,8 @@
       <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$79万
-$836/呎
+$879万
+$20,836/呎
 (在售)</t>
         </is>
       </c>
@@ -38204,8 +38204,8 @@
       <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$24万
-$521/呎
+$1024万
+$21,521/呎
 (在售)</t>
         </is>
       </c>
@@ -38249,8 +38249,8 @@
       <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$79万
-$836/呎
+$879万
+$20,836/呎
 (在售)</t>
         </is>
       </c>
@@ -38318,16 +38318,16 @@
       <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$76万
-$754/呎
+$876万
+$20,754/呎
 (在售)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$49万
-$192/呎
+$949万
+$21,192/呎
 (在售)</t>
         </is>
       </c>
@@ -38387,16 +38387,16 @@
       <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$74万
-$713/呎
+$874万
+$20,713/呎
 (在售)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$47万
-$129/呎
+$947万
+$21,129/呎
 (在售)</t>
         </is>
       </c>
@@ -38440,8 +38440,8 @@
       <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$57万
-$602/呎
+$657万
+$21,602/呎
 (在售)</t>
         </is>
       </c>
@@ -38456,16 +38456,16 @@
       <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$72万
-$671/呎
+$872万
+$20,671/呎
 (在售)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$44万
-$67/呎
+$944万
+$21,067/呎
 (在售)</t>
         </is>
       </c>
@@ -38480,8 +38480,8 @@
       <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$12万
-$265/呎
+$1012万
+$21,265/呎
 (在售)</t>
         </is>
       </c>
@@ -38509,8 +38509,8 @@
       <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$55万
-$539/呎
+$655万
+$21,539/呎
 (在售)</t>
         </is>
       </c>
@@ -38525,16 +38525,16 @@
       <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$71万
-$630/呎
+$871万
+$20,630/呎
 (在售)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$39万
-$960/呎
+$939万
+$20,960/呎
 (在售)</t>
         </is>
       </c>
@@ -38549,8 +38549,8 @@
       <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$7万
-$158/呎
+$1007万
+$21,158/呎
 (在售)</t>
         </is>
       </c>
@@ -38578,8 +38578,8 @@
       <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$53万
-$474/呎
+$653万
+$21,474/呎
 (在售)</t>
         </is>
       </c>
@@ -38594,16 +38594,16 @@
       <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$69万
-$588/呎
+$869万
+$20,588/呎
 (在售)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$32万
-$815/呎
+$932万
+$20,815/呎
 (在售)</t>
         </is>
       </c>
@@ -38618,8 +38618,8 @@
       <c r="I36" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$0万
-$11/呎
+$1000万
+$21,011/呎
 (在售)</t>
         </is>
       </c>
@@ -38663,16 +38663,16 @@
       <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$67万
-$547/呎
+$867万
+$20,547/呎
 (在售)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$18万
-$502/呎
+$918万
+$20,502/呎
 (在售)</t>
         </is>
       </c>
@@ -38732,16 +38732,16 @@
       <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$65万
-$505/呎
+$865万
+$20,505/呎
 (在售)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$96万
-$989/呎
+$896万
+$19,989/呎
 (在售)</t>
         </is>
       </c>
@@ -38801,16 +38801,16 @@
       <c r="F39" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$65万
-$505/呎
+$865万
+$20,505/呎
 (在售)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$96万
-$989/呎
+$896万
+$19,989/呎
 (在售)</t>
         </is>
       </c>
@@ -38854,8 +38854,8 @@
       <c r="D40" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$45万
-$217/呎
+$645万
+$21,217/呎
 (在售)</t>
         </is>
       </c>
@@ -38870,16 +38870,16 @@
       <c r="F40" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$62万
-$424/呎
+$862万
+$20,424/呎
 (在售)</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$90万
-$868/呎
+$890万
+$19,868/呎
 (在售)</t>
         </is>
       </c>
@@ -38894,8 +38894,8 @@
       <c r="I40" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$55万
-$57/呎
+$955万
+$20,057/呎
 (在售)</t>
         </is>
       </c>
@@ -38923,8 +38923,8 @@
       <c r="D41" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$39万
-$7/呎
+$639万
+$21,007/呎
 (在售)</t>
         </is>
       </c>
@@ -38939,16 +38939,16 @@
       <c r="F41" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$53万
-$220/呎
+$853万
+$20,220/呎
 (在售)</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$88万
-$810/呎
+$888万
+$19,810/呎
 (在售)</t>
         </is>
       </c>
@@ -38963,8 +38963,8 @@
       <c r="I41" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$52万
-$996/呎
+$952万
+$19,996/呎
 (在售)</t>
         </is>
       </c>
@@ -38992,8 +38992,8 @@
       <c r="D42" s="21" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$31万
-$747/呎
+$631万
+$20,747/呎
 (在售)</t>
         </is>
       </c>
@@ -39008,16 +39008,16 @@
       <c r="F42" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$32万
-$713/呎
+$832万
+$19,713/呎
 (在售)</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$82万
-$688/呎
+$882万
+$19,688/呎
 (在售)</t>
         </is>
       </c>
@@ -39032,8 +39032,8 @@
       <c r="I42" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
-$46万
-$876/呎
+$946万
+$19,876/呎
 (在售)</t>
         </is>
       </c>

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -641,7 +641,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -4896,22 +4896,18 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>12370680</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18887</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -5242,22 +5238,18 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>12333720</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18830</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -5588,22 +5580,18 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>12296760</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>18774</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -5934,22 +5922,18 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>12259800</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>18717</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6280,22 +6264,18 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>12223680</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>18662</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -6626,22 +6606,18 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>12186720</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>18606</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -6972,22 +6948,18 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>12150600</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>18551</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -7318,22 +7290,18 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>12150600</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>18551</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -7664,22 +7632,18 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>12078360</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>18440</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -9060,22 +9024,18 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>11922120</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>18146</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -9406,22 +9366,18 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>11897760</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18109</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -9752,22 +9708,18 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>11874240</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>18073</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -10168,22 +10120,18 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7568400</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>17935</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
@@ -10514,22 +10462,18 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>7545720</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>17881</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -10860,22 +10804,18 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>7523040</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>17827</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
@@ -11136,22 +11076,18 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>11779320</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>17929</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N152" s="3" t="inlineStr">
@@ -11202,22 +11138,18 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>7485240</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>17738</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -11478,22 +11410,18 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>11755800</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>17893</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -11544,22 +11472,18 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>7433160</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>17614</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N158" s="3" t="inlineStr">
@@ -11820,22 +11744,18 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>11732280</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>17857</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11886,22 +11806,18 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>7321440</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>17349</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -12232,22 +12148,18 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>7138320</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>16915</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -12578,22 +12490,18 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>7138320</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>16915</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12924,22 +12832,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>7095480</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>16814</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -13200,22 +13104,18 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>11639040</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>17715</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -13266,22 +13166,18 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>7074480</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>16764</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N183" s="3" t="inlineStr">
@@ -13542,22 +13438,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>11615520</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>17680</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -13608,22 +13500,18 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>7032480</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>16665</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -13884,22 +13772,18 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>11607120</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>17667</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -16190,22 +16074,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>7830480</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>18733</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -16746,22 +16626,18 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7807800</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>18679</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -17302,22 +17178,18 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>7784280</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>18623</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -17858,22 +17730,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>7760760</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>18566</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -18414,22 +18282,18 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>7737240</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>18510</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -18970,22 +18834,18 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>7714560</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>18456</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
@@ -19526,22 +19386,18 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>7714560</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>18456</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
@@ -20082,22 +19938,18 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>7668360</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>18345</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -20638,22 +20490,18 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>7645680</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>18291</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N289" s="3" t="inlineStr">
@@ -20774,22 +20622,18 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>5902680</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>19290</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
@@ -21190,22 +21034,18 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>7623000</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>18237</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N297" s="3" t="inlineStr">
@@ -21326,22 +21166,18 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K299" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L299" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K299" s="5" t="n">
+        <v>5885040</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>19232</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N299" s="3" t="inlineStr">
@@ -21742,22 +21578,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K305" s="5" t="n">
+        <v>7599480</v>
+      </c>
+      <c r="L305" s="5" t="n">
+        <v>18181</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -21878,22 +21710,18 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K307" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L307" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K307" s="5" t="n">
+        <v>5867400</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>19175</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N307" s="3" t="inlineStr">
@@ -22294,22 +22122,18 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K313" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L313" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K313" s="5" t="n">
+        <v>7576800</v>
+      </c>
+      <c r="L313" s="5" t="n">
+        <v>18126</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N313" s="3" t="inlineStr">
@@ -22430,22 +22254,18 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K315" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L315" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K315" s="5" t="n">
+        <v>5849760</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>19117</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N315" s="3" t="inlineStr">
@@ -22846,22 +22666,18 @@
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K321" s="5" t="n">
+        <v>7554120</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>18072</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N321" s="3" t="inlineStr">
@@ -22982,22 +22798,18 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>5832120</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>19059</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
@@ -23398,22 +23210,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K329" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L329" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K329" s="5" t="n">
+        <v>7531440</v>
+      </c>
+      <c r="L329" s="5" t="n">
+        <v>18018</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -23534,22 +23342,18 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K331" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L331" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K331" s="5" t="n">
+        <v>5814480</v>
+      </c>
+      <c r="L331" s="5" t="n">
+        <v>19002</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N331" s="3" t="inlineStr">
@@ -23950,22 +23754,18 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L337" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>7509600</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>17966</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N337" s="3" t="inlineStr">
@@ -24086,22 +23886,18 @@
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>5797680</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>18947</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N339" s="3" t="inlineStr">
@@ -24502,22 +24298,18 @@
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K345" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L345" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K345" s="5" t="n">
+        <v>7509600</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>17966</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N345" s="3" t="inlineStr">
@@ -24638,22 +24430,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K347" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L347" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K347" s="5" t="n">
+        <v>5797680</v>
+      </c>
+      <c r="L347" s="5" t="n">
+        <v>18947</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -25054,22 +24842,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K353" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L353" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K353" s="5" t="n">
+        <v>7464240</v>
+      </c>
+      <c r="L353" s="5" t="n">
+        <v>17857</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -25190,22 +24974,18 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K355" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L355" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K355" s="5" t="n">
+        <v>5763240</v>
+      </c>
+      <c r="L355" s="5" t="n">
+        <v>18834</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N355" s="3" t="inlineStr">
@@ -25606,22 +25386,18 @@
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K361" s="5" t="n">
+        <v>7460880</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>17680</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N361" s="3" t="inlineStr">
@@ -26162,22 +25938,18 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K369" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L369" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K369" s="5" t="n">
+        <v>7445760</v>
+      </c>
+      <c r="L369" s="5" t="n">
+        <v>17644</v>
       </c>
       <c r="M369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N369" s="3" t="inlineStr">
@@ -26718,22 +26490,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K377" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L377" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K377" s="5" t="n">
+        <v>7430640</v>
+      </c>
+      <c r="L377" s="5" t="n">
+        <v>17608</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -27064,22 +26832,18 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K382" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L382" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K382" s="5" t="n">
+        <v>8657040</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>18187</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
@@ -27270,22 +27034,18 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K385" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L385" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K385" s="5" t="n">
+        <v>7415520</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>17572</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N385" s="3" t="inlineStr">
@@ -27406,22 +27166,18 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K387" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L387" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K387" s="5" t="n">
+        <v>5617080</v>
+      </c>
+      <c r="L387" s="5" t="n">
+        <v>18477</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N387" s="3" t="inlineStr">
@@ -27612,22 +27368,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="n">
+        <v>8631000</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>18132</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -27818,22 +27570,18 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="n">
+        <v>7401240</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>17538</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N393" s="3" t="inlineStr">
@@ -27954,22 +27702,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K395" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L395" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K395" s="5" t="n">
+        <v>5600280</v>
+      </c>
+      <c r="L395" s="5" t="n">
+        <v>18422</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -28160,22 +27904,18 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K398" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L398" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K398" s="5" t="n">
+        <v>8604960</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>18078</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N398" s="3" t="inlineStr">
@@ -28366,22 +28106,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K401" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L401" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K401" s="5" t="n">
+        <v>7386120</v>
+      </c>
+      <c r="L401" s="5" t="n">
+        <v>17503</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -28502,22 +28238,18 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K403" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L403" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K403" s="5" t="n">
+        <v>5583480</v>
+      </c>
+      <c r="L403" s="5" t="n">
+        <v>18367</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N403" s="3" t="inlineStr">
@@ -28918,22 +28650,18 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K409" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L409" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K409" s="5" t="n">
+        <v>7386120</v>
+      </c>
+      <c r="L409" s="5" t="n">
+        <v>17503</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -29404,22 +29132,18 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>7974960</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>17801</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N416" s="3" t="inlineStr">
@@ -29470,22 +29194,18 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>7356720</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>17433</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N417" s="3" t="inlineStr">
@@ -29956,22 +29676,18 @@
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K424" s="5" t="n">
+        <v>7951440</v>
+      </c>
+      <c r="L424" s="5" t="n">
+        <v>17749</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N424" s="3" t="inlineStr">
@@ -30022,22 +29738,18 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K425" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L425" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K425" s="5" t="n">
+        <v>7342440</v>
+      </c>
+      <c r="L425" s="5" t="n">
+        <v>17399</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N425" s="3" t="inlineStr">
@@ -30368,22 +30080,18 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K430" s="5" t="n">
+        <v>8502480</v>
+      </c>
+      <c r="L430" s="5" t="n">
+        <v>17862</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -30504,22 +30212,18 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K432" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L432" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K432" s="5" t="n">
+        <v>7927920</v>
+      </c>
+      <c r="L432" s="5" t="n">
+        <v>17696</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N432" s="3" t="inlineStr">
@@ -30570,22 +30274,18 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K433" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L433" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K433" s="5" t="n">
+        <v>7327320</v>
+      </c>
+      <c r="L433" s="5" t="n">
+        <v>17363</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -30706,22 +30406,18 @@
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K435" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L435" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K435" s="5" t="n">
+        <v>5516280</v>
+      </c>
+      <c r="L435" s="5" t="n">
+        <v>18146</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N435" s="3" t="inlineStr">
@@ -30912,22 +30608,18 @@
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K438" s="5" t="n">
+        <v>8459640</v>
+      </c>
+      <c r="L438" s="5" t="n">
+        <v>17772</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N438" s="3" t="inlineStr">
@@ -31048,22 +30740,18 @@
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K440" s="5" t="n">
+        <v>7887600</v>
+      </c>
+      <c r="L440" s="5" t="n">
+        <v>17606</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N440" s="3" t="inlineStr">
@@ -31114,22 +30802,18 @@
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K441" s="5" t="n">
+        <v>7313040</v>
+      </c>
+      <c r="L441" s="5" t="n">
+        <v>17329</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N441" s="3" t="inlineStr">
@@ -31250,22 +30934,18 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K443" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L443" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K443" s="5" t="n">
+        <v>5500320</v>
+      </c>
+      <c r="L443" s="5" t="n">
+        <v>18093</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N443" s="3" t="inlineStr">
@@ -31456,22 +31136,18 @@
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K446" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L446" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K446" s="5" t="n">
+        <v>8400840</v>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>17649</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N446" s="3" t="inlineStr">
@@ -31592,22 +31268,18 @@
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K448" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L448" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K448" s="5" t="n">
+        <v>7833000</v>
+      </c>
+      <c r="L448" s="5" t="n">
+        <v>17484</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N448" s="3" t="inlineStr">
@@ -31658,22 +31330,18 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K449" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L449" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K449" s="5" t="n">
+        <v>7297920</v>
+      </c>
+      <c r="L449" s="5" t="n">
+        <v>17294</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N449" s="3" t="inlineStr">
@@ -31794,22 +31462,18 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K451" s="5" t="n">
+        <v>5483520</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>18038</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N451" s="3" t="inlineStr">
@@ -32140,22 +31804,18 @@
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K456" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L456" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K456" s="5" t="n">
+        <v>7715400</v>
+      </c>
+      <c r="L456" s="5" t="n">
+        <v>17222</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N456" s="3" t="inlineStr">
@@ -32206,22 +31866,18 @@
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K457" s="5" t="n">
+        <v>7283640</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>17260</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N457" s="3" t="inlineStr">
@@ -32692,22 +32348,18 @@
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K464" s="5" t="n">
+        <v>7522200</v>
+      </c>
+      <c r="L464" s="5" t="n">
+        <v>16791</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N464" s="3" t="inlineStr">
@@ -32758,22 +32410,18 @@
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K465" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L465" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K465" s="5" t="n">
+        <v>7268520</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>17224</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N465" s="3" t="inlineStr">
@@ -33244,22 +32892,18 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K472" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L472" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K472" s="5" t="n">
+        <v>7522200</v>
+      </c>
+      <c r="L472" s="5" t="n">
+        <v>16791</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N472" s="3" t="inlineStr">
@@ -33310,22 +32954,18 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K473" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L473" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K473" s="5" t="n">
+        <v>7268520</v>
+      </c>
+      <c r="L473" s="5" t="n">
+        <v>17224</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N473" s="3" t="inlineStr">
@@ -33656,22 +33296,18 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K478" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L478" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K478" s="5" t="n">
+        <v>8019480</v>
+      </c>
+      <c r="L478" s="5" t="n">
+        <v>16848</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N478" s="3" t="inlineStr">
@@ -33792,22 +33428,18 @@
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K480" s="5" t="n">
+        <v>7476840</v>
+      </c>
+      <c r="L480" s="5" t="n">
+        <v>16689</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N480" s="3" t="inlineStr">
@@ -33858,22 +33490,18 @@
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K481" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L481" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K481" s="5" t="n">
+        <v>7239960</v>
+      </c>
+      <c r="L481" s="5" t="n">
+        <v>17156</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N481" s="3" t="inlineStr">
@@ -33994,22 +33622,18 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K483" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L483" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K483" s="5" t="n">
+        <v>5418000</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>17822</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N483" s="3" t="inlineStr">
@@ -34200,22 +33824,18 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K486" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L486" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K486" s="5" t="n">
+        <v>7995120</v>
+      </c>
+      <c r="L486" s="5" t="n">
+        <v>16796</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N486" s="3" t="inlineStr">
@@ -34336,22 +33956,18 @@
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K488" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L488" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K488" s="5" t="n">
+        <v>7455000</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>16641</v>
       </c>
       <c r="M488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N488" s="3" t="inlineStr">
@@ -34402,22 +34018,18 @@
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K489" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L489" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K489" s="5" t="n">
+        <v>7167720</v>
+      </c>
+      <c r="L489" s="5" t="n">
+        <v>16985</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N489" s="3" t="inlineStr">
@@ -34538,22 +34150,18 @@
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K491" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L491" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K491" s="5" t="n">
+        <v>5364240</v>
+      </c>
+      <c r="L491" s="5" t="n">
+        <v>17646</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N491" s="3" t="inlineStr">
@@ -34744,22 +34352,18 @@
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K494" s="5" t="n">
+        <v>7947240</v>
+      </c>
+      <c r="L494" s="5" t="n">
+        <v>16696</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N494" s="3" t="inlineStr">
@@ -34880,22 +34484,18 @@
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K496" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L496" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K496" s="5" t="n">
+        <v>7408800</v>
+      </c>
+      <c r="L496" s="5" t="n">
+        <v>16538</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N496" s="3" t="inlineStr">
@@ -34946,22 +34546,18 @@
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K497" s="5" t="n">
+        <v>6987960</v>
+      </c>
+      <c r="L497" s="5" t="n">
+        <v>16559</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N497" s="3" t="inlineStr">
@@ -35082,22 +34678,18 @@
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K499" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L499" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K499" s="5" t="n">
+        <v>5297880</v>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>17427</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N499" s="3" t="inlineStr">

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1808,34 +1808,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H18" s="5" t="n">
+        <v>10639000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>25151</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>8936760</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21127</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2080,7 +2072,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2088,34 +2080,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H22" s="5" t="n">
+        <v>15756000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>24055</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>13235040</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>20206</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2150,7 +2134,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2158,34 +2142,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H23" s="5" t="n">
+        <v>10533000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>24901</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>8847720</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>20917</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2430,7 +2406,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2438,34 +2414,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H27" s="5" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>23817</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>13104000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>20006</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2500,7 +2468,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2508,34 +2476,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H28" s="5" t="n">
+        <v>10429000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>24655</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>8760360</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>20710</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2780,7 +2740,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2788,34 +2748,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>15445000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>23580</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>12973800</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>19807</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2850,7 +2802,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2858,34 +2810,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>10326000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>24411</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>8673840</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20506</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3130,7 +3074,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3138,34 +3082,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>15292000</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>23347</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>12845280</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>19611</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3200,7 +3136,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3208,34 +3144,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>10224000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>24170</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>8588160</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>20303</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3480,7 +3408,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3488,34 +3416,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H42" s="5" t="n">
+        <v>15141000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>23116</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>12718440</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>19417</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3550,7 +3470,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3558,34 +3478,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>10122000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>23929</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8502480</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>20100</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3830,7 +3742,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3838,34 +3750,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H47" s="5" t="n">
+        <v>14991000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>22887</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>12592440</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>19225</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3900,7 +3804,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3908,34 +3812,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H48" s="5" t="n">
+        <v>10122000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>23929</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>8502480</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>20100</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -4180,7 +4076,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4188,34 +4084,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H52" s="5" t="n">
+        <v>14902000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>22751</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>12517680</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>19111</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -4250,7 +4138,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4258,34 +4146,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>10002000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>23645</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8401680</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>19862</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4530,7 +4410,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4538,34 +4418,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H57" s="5" t="n">
+        <v>14813000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>22615</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>12442920</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>18997</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -4600,7 +4472,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4608,34 +4480,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H58" s="5" t="n">
+        <v>9943000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>23506</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>8352120</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>19745</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -4942,7 +4806,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4950,34 +4814,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>9883000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>23364</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>8301720</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>19626</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -5284,7 +5140,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5292,34 +5148,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H68" s="5" t="n">
+        <v>9824000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>23225</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>8252160</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>19509</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -5626,7 +5474,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5634,34 +5482,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>9766000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>23087</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>8203440</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>19393</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5968,7 +5808,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5976,34 +5816,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>9708000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>22950</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>8154720</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>19278</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -6310,7 +6142,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6318,34 +6150,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>9650000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>22813</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8106000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>19163</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6652,7 +6476,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6660,34 +6484,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>9592000</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>22676</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>8057280</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>19048</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6994,7 +6810,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7002,34 +6818,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>9592000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>22676</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>8057280</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19048</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -7336,7 +7144,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7344,34 +7152,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H98" s="5" t="n">
+        <v>9478000</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>22407</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7961520</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18822</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -7678,7 +7478,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7686,34 +7486,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>9361000</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>22182</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>7863240</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>18633</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -7958,7 +7750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7966,34 +7758,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>14278000</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>21732</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>11993520</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>18255</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -8028,7 +7812,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -8036,34 +7820,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>9174000</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>21739</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>7706160</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>18261</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
@@ -8308,7 +8084,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8316,34 +8092,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>14250000</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>21689</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>11970000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>18219</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -8378,7 +8146,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8386,34 +8154,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>9147000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>21675</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7683480</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>18207</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8658,7 +8418,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8666,34 +8426,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>14221000</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>21645</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>11945640</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>18182</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8728,7 +8480,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8736,34 +8488,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>9119000</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>21609</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>7659960</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18152</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -9070,7 +8814,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -9078,34 +8822,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H123" s="5" t="n">
+        <v>9092000</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>21545</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>7637280</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>18098</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
@@ -9412,7 +9148,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9420,34 +9156,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H128" s="5" t="n">
+        <v>9065000</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>21481</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7614600</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>18044</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
@@ -9754,7 +9482,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9762,34 +9490,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H133" s="5" t="n">
+        <v>9065000</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>21481</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>7614600</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>18044</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -10034,7 +9754,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -10042,34 +9762,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>14136000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>21516</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>11874240</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>18073</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -10376,7 +10088,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10384,34 +10096,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>14080000</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>21431</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>11827200</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>18002</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -10718,7 +10422,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10726,34 +10430,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>14051000</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>21387</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>11802840</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>17965</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
@@ -12062,7 +11758,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -12070,34 +11766,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H167" s="5" t="n">
+        <v>13939000</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>21216</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>11708760</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>17822</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -12404,7 +12092,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12412,34 +12100,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H172" s="5" t="n">
+        <v>13911000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>21174</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>11685240</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>17786</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -12746,7 +12426,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12754,34 +12434,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>13911000</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>21174</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>11685240</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>17786</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -15988,7 +15660,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15996,34 +15668,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>11219000</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>24931</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>9423960</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>20942</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -16540,7 +16204,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -16548,34 +16212,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H232" s="5" t="n">
+        <v>11108000</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>24684</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>9330720</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>20735</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -17092,7 +16748,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -17100,34 +16756,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H240" s="5" t="n">
+        <v>10998000</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>24440</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>9238320</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>20530</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -17644,7 +17292,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17652,34 +17300,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H248" s="5" t="n">
+        <v>10889000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>24198</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>9146760</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>20326</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -18196,7 +17836,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -18204,34 +17844,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H256" s="5" t="n">
+        <v>10781000</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>23958</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>9056040</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>20125</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
@@ -18398,7 +18030,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18406,34 +18038,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H259" s="5" t="n">
+        <v>7117000</v>
+      </c>
+      <c r="I259" s="5" t="n">
+        <v>23258</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>5978280</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>19537</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -18748,7 +18372,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -18756,34 +18380,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H264" s="5" t="n">
+        <v>10675000</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>23722</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>19927</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
@@ -18950,7 +18566,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18958,34 +18574,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H267" s="5" t="n">
+        <v>7096000</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>23190</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>5960640</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>19479</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -19300,7 +18908,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -19308,34 +18916,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H272" s="5" t="n">
+        <v>10675000</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>23722</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>19927</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
@@ -19502,7 +19102,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -19510,34 +19110,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H275" s="5" t="n">
+        <v>7096000</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>23190</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>5960640</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>19479</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -19852,7 +19444,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -19860,34 +19452,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H280" s="5" t="n">
+        <v>10548000</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>23440</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>8860320</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>19690</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
@@ -20054,7 +19638,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -20062,34 +19646,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H283" s="5" t="n">
+        <v>7054000</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>23052</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>5925360</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>19364</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
@@ -20404,7 +19980,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -20412,34 +19988,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H288" s="5" t="n">
+        <v>10485000</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>23300</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>8807400</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>19572</v>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
@@ -20948,7 +20516,7 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -20956,34 +20524,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H296" s="5" t="n">
+        <v>10423000</v>
+      </c>
+      <c r="I296" s="5" t="n">
+        <v>23162</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K296" s="5" t="n">
+        <v>8755320</v>
+      </c>
+      <c r="L296" s="5" t="n">
+        <v>19456</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N296" s="3" t="inlineStr">
@@ -21492,7 +21052,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -21500,34 +21060,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H304" s="5" t="n">
+        <v>10361000</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>23024</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K304" s="5" t="n">
+        <v>8703240</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>19341</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N304" s="3" t="inlineStr">
@@ -22036,7 +21588,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -22044,34 +21596,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H312" s="5" t="n">
+        <v>10299000</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>22887</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="n">
+        <v>8651160</v>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>19225</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -22580,7 +22124,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -22588,34 +22132,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H320" s="5" t="n">
+        <v>10237000</v>
+      </c>
+      <c r="I320" s="5" t="n">
+        <v>22749</v>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K320" s="5" t="n">
+        <v>8599080</v>
+      </c>
+      <c r="L320" s="5" t="n">
+        <v>19109</v>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -23124,7 +22660,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -23132,34 +22668,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H328" s="5" t="n">
+        <v>10176000</v>
+      </c>
+      <c r="I328" s="5" t="n">
+        <v>22613</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K328" s="5" t="n">
+        <v>8547840</v>
+      </c>
+      <c r="L328" s="5" t="n">
+        <v>18995</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N328" s="3" t="inlineStr">
@@ -23668,7 +23196,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -23676,34 +23204,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H336" s="5" t="n">
+        <v>10129000</v>
+      </c>
+      <c r="I336" s="5" t="n">
+        <v>22509</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K336" s="5" t="n">
+        <v>8508360</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>18907</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N336" s="3" t="inlineStr">
@@ -24212,7 +23732,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -24220,34 +23740,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H344" s="5" t="n">
+        <v>10129000</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>22509</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K344" s="5" t="n">
+        <v>8508360</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>18907</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N344" s="3" t="inlineStr">
@@ -24756,7 +24268,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -24764,34 +24276,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H352" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I352" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H352" s="5" t="n">
+        <v>10009000</v>
+      </c>
+      <c r="I352" s="5" t="n">
+        <v>22242</v>
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K352" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L352" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K352" s="5" t="n">
+        <v>8407560</v>
+      </c>
+      <c r="L352" s="5" t="n">
+        <v>18683</v>
       </c>
       <c r="M352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N352" s="3" t="inlineStr">
@@ -25160,7 +24664,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -25168,34 +24672,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H358" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I358" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H358" s="5" t="n">
+        <v>10580000</v>
+      </c>
+      <c r="I358" s="5" t="n">
+        <v>22227</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K358" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L358" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K358" s="5" t="n">
+        <v>8887200</v>
+      </c>
+      <c r="L358" s="5" t="n">
+        <v>18671</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -25300,7 +24796,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -25308,34 +24804,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H360" s="5" t="n">
+        <v>9864000</v>
+      </c>
+      <c r="I360" s="5" t="n">
+        <v>22018</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K360" s="5" t="n">
+        <v>8285760</v>
+      </c>
+      <c r="L360" s="5" t="n">
+        <v>18495</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -25712,7 +25200,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -25720,34 +25208,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H366" s="5" t="n">
+        <v>10368000</v>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>21782</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K366" s="5" t="n">
+        <v>8709120</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>18296</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -25852,7 +25332,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -25860,34 +25340,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H368" s="5" t="n">
+        <v>9667000</v>
+      </c>
+      <c r="I368" s="5" t="n">
+        <v>21578</v>
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K368" s="5" t="n">
+        <v>8120280</v>
+      </c>
+      <c r="L368" s="5" t="n">
+        <v>18126</v>
       </c>
       <c r="M368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N368" s="3" t="inlineStr">
@@ -26264,7 +25736,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -26272,34 +25744,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H374" s="5" t="n">
+        <v>10337000</v>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>21716</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K374" s="5" t="n">
+        <v>8683080</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>18242</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N374" s="3" t="inlineStr">
@@ -26404,7 +25868,7 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -26412,34 +25876,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H376" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I376" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H376" s="5" t="n">
+        <v>9638000</v>
+      </c>
+      <c r="I376" s="5" t="n">
+        <v>21513</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K376" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L376" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K376" s="5" t="n">
+        <v>8095920</v>
+      </c>
+      <c r="L376" s="5" t="n">
+        <v>18071</v>
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N376" s="3" t="inlineStr">
@@ -26948,7 +26404,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -26956,34 +26412,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H384" s="5" t="n">
+        <v>9609000</v>
+      </c>
+      <c r="I384" s="5" t="n">
+        <v>21449</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K384" s="5" t="n">
+        <v>8071560</v>
+      </c>
+      <c r="L384" s="5" t="n">
+        <v>18017</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -27484,7 +26932,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -27492,34 +26940,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H392" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H392" s="5" t="n">
+        <v>9580000</v>
+      </c>
+      <c r="I392" s="5" t="n">
+        <v>21384</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K392" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L392" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K392" s="5" t="n">
+        <v>8047200</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>17962</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N392" s="3" t="inlineStr">
@@ -28020,7 +27460,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -28028,34 +27468,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H400" s="5" t="n">
+        <v>9552000</v>
+      </c>
+      <c r="I400" s="5" t="n">
+        <v>21321</v>
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K400" s="5" t="n">
+        <v>8023680</v>
+      </c>
+      <c r="L400" s="5" t="n">
+        <v>17910</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N400" s="3" t="inlineStr">
@@ -28424,7 +27856,7 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -28432,34 +27864,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H406" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I406" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H406" s="5" t="n">
+        <v>10244000</v>
+      </c>
+      <c r="I406" s="5" t="n">
+        <v>21521</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K406" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L406" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K406" s="5" t="n">
+        <v>8604960</v>
+      </c>
+      <c r="L406" s="5" t="n">
+        <v>18078</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N406" s="3" t="inlineStr">
@@ -28564,7 +27988,7 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -28572,34 +27996,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H408" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I408" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H408" s="5" t="n">
+        <v>9552000</v>
+      </c>
+      <c r="I408" s="5" t="n">
+        <v>21321</v>
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K408" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L408" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K408" s="5" t="n">
+        <v>8023680</v>
+      </c>
+      <c r="L408" s="5" t="n">
+        <v>17910</v>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N408" s="3" t="inlineStr">
@@ -28976,7 +28392,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -28984,34 +28400,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H414" s="5" t="n">
+        <v>10183000</v>
+      </c>
+      <c r="I414" s="5" t="n">
+        <v>21393</v>
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K414" s="5" t="n">
+        <v>8553720</v>
+      </c>
+      <c r="L414" s="5" t="n">
+        <v>17970</v>
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -29520,7 +28928,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -29528,34 +28936,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H422" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I422" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H422" s="5" t="n">
+        <v>10152000</v>
+      </c>
+      <c r="I422" s="5" t="n">
+        <v>21328</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K422" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L422" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K422" s="5" t="n">
+        <v>8527680</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>17915</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N422" s="3" t="inlineStr">
@@ -31648,7 +31048,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -31656,34 +31056,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H454" s="5" t="n">
+        <v>9851000</v>
+      </c>
+      <c r="I454" s="5" t="n">
+        <v>20695</v>
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K454" s="5" t="n">
+        <v>8274840</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>17384</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -32192,7 +31584,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -32200,34 +31592,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H462" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I462" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H462" s="5" t="n">
+        <v>9614000</v>
+      </c>
+      <c r="I462" s="5" t="n">
+        <v>20197</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K462" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L462" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K462" s="5" t="n">
+        <v>8075760</v>
+      </c>
+      <c r="L462" s="5" t="n">
+        <v>16966</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N462" s="3" t="inlineStr">
@@ -32736,7 +32120,7 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -32744,34 +32128,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H470" s="5" t="n">
+        <v>9614000</v>
+      </c>
+      <c r="I470" s="5" t="n">
+        <v>20197</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K470" s="5" t="n">
+        <v>8075760</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>16966</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90 天現金付款計劃</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
@@ -35476,7 +34852,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -35491,7 +34867,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -35674,44 +35050,44 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1576万
+$24,055/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1064万
+$25,151/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35721,44 +35097,44 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1560万
+$23,817/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1053万
+$24,901/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35768,44 +35144,44 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1544万
+$23,580/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1043万
+$24,655/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35815,44 +35191,44 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1529万
+$23,347/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1033万
+$24,411/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35862,44 +35238,44 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1514万
+$23,116/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1022万
+$24,170/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35909,44 +35285,44 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1499万
+$22,887/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1012万
+$23,929/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -35956,44 +35332,44 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1490万
+$22,751/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1012万
+$23,929/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36003,44 +35379,44 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+$1481万
+$22,615/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$1000万
+$23,645/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36082,12 +35458,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$994万
+$23,506/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36129,12 +35505,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$988万
+$23,364/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36176,12 +35552,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$982万
+$23,225/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36223,12 +35599,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$977万
+$23,087/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36270,12 +35646,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$971万
+$22,950/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36317,12 +35693,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$965万
+$22,813/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36364,12 +35740,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$959万
+$22,676/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36411,12 +35787,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$959万
+$22,676/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36458,12 +35834,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+$948万
+$22,407/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36473,44 +35849,44 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
+$1428万
+$21,732/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$936万
+$22,182/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36520,44 +35896,44 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
+$1425万
+$21,689/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$917万
+$21,739/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36567,44 +35943,44 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
+$1422万
+$21,645/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$915万
+$21,675/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36646,12 +36022,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$912万
+$21,609/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36693,12 +36069,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$909万
+$21,545/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36740,12 +36116,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$906万
+$21,481/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36755,44 +36131,44 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
+$1414万
+$21,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
--
--
-(待售)</t>
+$906万
+$21,481/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36802,12 +36178,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
--
--
-(待售)</t>
+$1408万
+$21,431/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -36849,12 +36225,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
--
--
-(待售)</t>
+$1405万
+$21,387/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -37037,12 +36413,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
--
--
-(待售)</t>
+$1394万
+$21,216/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -37084,12 +36460,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
--
--
-(待售)</t>
+$1391万
+$21,174/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -37131,12 +36507,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
--
--
-(待售)</t>
+$1391万
+$21,174/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -37441,7 +36817,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -37456,7 +36832,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>202</t>
         </is>
       </c>
     </row>
@@ -37766,12 +37142,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1122万
+$24,931/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -37837,12 +37213,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1111万
+$24,684/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -37908,12 +37284,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1100万
+$24,440/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -37979,12 +37355,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1089万
+$24,198/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -38026,12 +37402,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
--
--
-(待售)</t>
+$712万
+$23,258/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -38050,12 +37426,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1078万
+$23,958/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -38097,12 +37473,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
--
--
-(待售)</t>
+$710万
+$23,190/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -38121,12 +37497,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1068万
+$23,722/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -38168,12 +37544,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
--
--
-(待售)</t>
+$710万
+$23,190/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -38192,12 +37568,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1068万
+$23,722/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -38239,12 +37615,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
--
--
-(待售)</t>
+$705万
+$23,052/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -38263,12 +37639,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1055万
+$23,440/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -38334,12 +37710,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1048万
+$23,300/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -38405,12 +37781,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1042万
+$23,162/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -38476,12 +37852,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1036万
+$23,024/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -38547,12 +37923,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1030万
+$22,887/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -38618,12 +37994,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1024万
+$22,749/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -38689,12 +38065,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1018万
+$22,613/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -38760,12 +38136,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1013万
+$22,509/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -38831,12 +38207,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1013万
+$22,509/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -38902,12 +38278,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
--
--
-(待售)</t>
+$1001万
+$22,242/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -38973,28 +38349,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
+$986万
+$22,018/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1058万
+$22,227/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39044,28 +38420,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
+$967万
+$21,578/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1037万
+$21,782/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39115,28 +38491,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
+$964万
+$21,513/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1034万
+$21,716/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39186,12 +38562,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
--
--
-(待售)</t>
+$961万
+$21,449/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -39257,12 +38633,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
--
--
-(待售)</t>
+$958万
+$21,384/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -39328,12 +38704,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
--
--
-(待售)</t>
+$955万
+$21,321/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -39399,28 +38775,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
+$955万
+$21,321/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1024万
+$21,521/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39486,12 +38862,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1018万
+$21,393/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39557,12 +38933,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I33" s="20" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$1015万
+$21,328/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39841,12 +39217,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I37" s="20" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$985万
+$20,695/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39912,12 +39288,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$961万
+$20,197/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39983,12 +39359,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I39" s="20" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
--
--
-(待售)</t>
+$961万
+$20,197/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="00002060"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +265,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4868,7 +4877,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4878,12 +4887,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -4893,12 +4902,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -4908,7 +4917,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4947,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4948,12 +4957,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -4963,12 +4972,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -4978,7 +4987,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5211,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5212,12 +5221,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -5227,12 +5236,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5242,7 +5251,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5281,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5282,12 +5291,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -5297,12 +5306,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -5312,7 +5321,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5545,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5546,12 +5555,12 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -5561,12 +5570,12 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -5576,7 +5585,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5615,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5616,12 +5625,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5631,12 +5640,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5646,7 +5655,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5879,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5880,12 +5889,12 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -5895,12 +5904,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -5910,7 +5919,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5949,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -5950,12 +5959,12 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -5965,12 +5974,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -5980,7 +5989,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6213,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6214,12 +6223,12 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -6229,12 +6238,12 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -6244,7 +6253,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6283,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6284,12 +6293,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -6299,12 +6308,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -6314,7 +6323,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6547,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6548,12 +6557,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -6563,12 +6572,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -6578,7 +6587,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6617,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6618,12 +6627,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -6633,12 +6642,12 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -6648,7 +6657,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6881,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -6882,12 +6891,12 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -6897,12 +6906,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -6912,7 +6921,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6951,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -6952,12 +6961,12 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -6967,12 +6976,12 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
@@ -6982,7 +6991,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7215,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7216,12 +7225,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -7231,12 +7240,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -7246,7 +7255,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7285,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7286,12 +7295,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -7301,12 +7310,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -7316,7 +7325,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7549,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7550,12 +7559,12 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -7565,12 +7574,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
@@ -7580,7 +7589,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7619,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7620,12 +7629,12 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
@@ -7635,12 +7644,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -7650,7 +7659,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7883,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7884,12 +7893,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -7899,12 +7908,12 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M109" s="3" t="inlineStr">
@@ -7914,7 +7923,7 @@
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7953,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -7954,12 +7963,12 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
@@ -7969,12 +7978,12 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
@@ -7984,7 +7993,7 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13779,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13780,12 +13789,12 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr">
@@ -13795,12 +13804,12 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
@@ -13810,7 +13819,7 @@
       </c>
       <c r="N197" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34847,27 +34856,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -35489,20 +35498,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -35536,20 +35545,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -35583,20 +35592,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -35630,20 +35639,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -35677,20 +35686,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -35724,20 +35733,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -35771,20 +35780,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -35818,20 +35827,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -35865,20 +35874,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -35912,20 +35921,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -36695,12 +36704,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>A | 619呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -127,13 +127,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -272,10 +272,10 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4781,38 +4781,30 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>16900000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>25000</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K64" s="5" t="n">
+        <v>16900000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>25000</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4821,7 +4813,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5107,38 +5099,30 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>16833000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>24901</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K69" s="5" t="n">
+        <v>16833000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>24901</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -5147,7 +5131,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5433,38 +5417,30 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>16765000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>24800</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K74" s="5" t="n">
+        <v>16765000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>24800</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5473,7 +5449,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5503,38 +5479,30 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>14150000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>25313</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K75" s="5" t="n">
+        <v>14150000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>25313</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5543,7 +5511,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5759,38 +5727,30 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>16698000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>24701</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K79" s="5" t="n">
+        <v>16698000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>24701</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5799,7 +5759,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5829,38 +5789,30 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>14087000</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>25200</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K80" s="5" t="n">
+        <v>14087000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>25200</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5869,7 +5821,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6085,38 +6037,30 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>16629600</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>24600</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K84" s="5" t="n">
+        <v>16629600</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>24600</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6125,7 +6069,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6155,38 +6099,30 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>13975000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>25000</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K85" s="5" t="n">
+        <v>13975000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>25000</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6195,7 +6131,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6411,38 +6347,30 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>16157000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>23901</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K89" s="5" t="n">
+        <v>16157000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>23901</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6451,7 +6379,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6737,38 +6665,30 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>16143000</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>23880</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K94" s="5" t="n">
+        <v>16143000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>23880</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6777,7 +6697,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7063,38 +6983,30 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>16785000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>24830</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K99" s="5" t="n">
+        <v>16785000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>24830</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7103,7 +7015,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7133,38 +7045,30 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>13416000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K100" s="5" t="n">
+        <v>13416000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7173,7 +7077,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7389,38 +7293,30 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>23529</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K104" s="5" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>23529</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7429,7 +7325,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7459,38 +7355,30 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>13480000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>24158</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K105" s="5" t="n">
+        <v>13480000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>24158</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7499,7 +7387,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7715,38 +7603,30 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>15640000</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>23000</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K109" s="5" t="n">
+        <v>15640000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>23000</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -7755,7 +7635,7 @@
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7785,38 +7665,30 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>14361800</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>25738</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K110" s="5" t="n">
+        <v>14361800</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>25738</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7825,7 +7697,7 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8041,7 +7913,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8051,12 +7923,12 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -8066,12 +7938,12 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
@@ -8081,7 +7953,7 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8111,7 +7983,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8121,12 +7993,12 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -8136,12 +8008,12 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
@@ -8151,7 +8023,7 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8239,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8377,12 +8249,12 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -8392,12 +8264,12 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
@@ -8407,7 +8279,7 @@
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8309,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8447,12 +8319,12 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
@@ -8462,12 +8334,12 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M120" s="3" t="inlineStr">
@@ -8477,7 +8349,7 @@
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8565,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8703,12 +8575,12 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -8718,12 +8590,12 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
@@ -8733,7 +8605,7 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8635,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8773,12 +8645,12 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
@@ -8788,12 +8660,12 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M125" s="3" t="inlineStr">
@@ -8803,7 +8675,7 @@
       </c>
       <c r="N125" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9019,7 +8891,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9029,12 +8901,12 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -9044,12 +8916,12 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
@@ -9059,7 +8931,7 @@
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9089,7 +8961,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9099,12 +8971,12 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -9114,12 +8986,12 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
@@ -9129,7 +9001,7 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9217,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9355,12 +9227,12 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -9370,12 +9242,12 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
@@ -9385,7 +9257,7 @@
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9287,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9425,12 +9297,12 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -9440,12 +9312,12 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
@@ -9455,7 +9327,7 @@
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13137,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -13275,12 +13147,12 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -13290,12 +13162,12 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
@@ -13305,7 +13177,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13207,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13345,12 +13217,12 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr">
@@ -13360,12 +13232,12 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
@@ -13375,7 +13247,7 @@
       </c>
       <c r="N195" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13277,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -13415,12 +13287,12 @@
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr">
@@ -13430,12 +13302,12 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
@@ -13445,7 +13317,7 @@
       </c>
       <c r="N196" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13475,38 +13347,30 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I197" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>14856000</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K197" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L197" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K197" s="5" t="n">
+        <v>14856000</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -13515,7 +13379,7 @@
       </c>
       <c r="N197" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14419,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14565,12 +14429,12 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J213" s="3" t="inlineStr">
@@ -14580,12 +14444,12 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
@@ -14595,7 +14459,7 @@
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15075,7 +14939,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15085,12 +14949,12 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J221" s="3" t="inlineStr">
@@ -15100,12 +14964,12 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
@@ -15115,7 +14979,7 @@
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15459,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15605,12 +15469,12 @@
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
@@ -15620,12 +15484,12 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
@@ -15635,7 +15499,7 @@
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16115,7 +15979,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16125,12 +15989,12 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr">
@@ -16140,12 +16004,12 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
@@ -16155,7 +16019,7 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16499,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16645,12 +16509,12 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J245" s="3" t="inlineStr">
@@ -16660,12 +16524,12 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
@@ -16675,7 +16539,7 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17019,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -17165,12 +17029,12 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J253" s="3" t="inlineStr">
@@ -17180,12 +17044,12 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
@@ -17195,7 +17059,7 @@
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17539,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17685,12 +17549,12 @@
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J261" s="3" t="inlineStr">
@@ -17700,12 +17564,12 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
@@ -17715,7 +17579,7 @@
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18059,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -18205,12 +18069,12 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J269" s="3" t="inlineStr">
@@ -18220,12 +18084,12 @@
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
@@ -18235,7 +18099,7 @@
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18579,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -18725,12 +18589,12 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J277" s="3" t="inlineStr">
@@ -18740,12 +18604,12 @@
       </c>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
@@ -18755,7 +18619,7 @@
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19099,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -19245,12 +19109,12 @@
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J285" s="3" t="inlineStr">
@@ -19260,12 +19124,12 @@
       </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
@@ -19275,7 +19139,7 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19755,7 +19619,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -19765,12 +19629,12 @@
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J293" s="3" t="inlineStr">
@@ -19780,12 +19644,12 @@
       </c>
       <c r="K293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
@@ -19795,7 +19659,7 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20275,7 +20139,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -20285,12 +20149,12 @@
       </c>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I301" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J301" s="3" t="inlineStr">
@@ -20300,12 +20164,12 @@
       </c>
       <c r="K301" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L301" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M301" s="3" t="inlineStr">
@@ -20315,7 +20179,7 @@
       </c>
       <c r="N301" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33193,7 +33057,7 @@
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -33203,12 +33067,12 @@
       </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J502" s="3" t="inlineStr">
@@ -33218,12 +33082,12 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M502" s="3" t="inlineStr">
@@ -33233,7 +33097,7 @@
       </c>
       <c r="N502" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33800,7 +33664,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33810,7 +33674,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33820,7 +33684,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -33933,12 +33797,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -33980,12 +33844,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -34003,7 +33867,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1450万
@@ -34027,15 +33891,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $979万
@@ -34050,7 +33914,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1435万
@@ -34074,15 +33938,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $969万
@@ -34097,7 +33961,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1297万
@@ -34121,15 +33985,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $960万
@@ -34144,7 +34008,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1407万
@@ -34168,15 +34032,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $950万
@@ -34191,7 +34055,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1393万
@@ -34215,15 +34079,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $859万
@@ -34238,7 +34102,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1259万
@@ -34262,15 +34126,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $931万
@@ -34285,7 +34149,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1371万
@@ -34309,15 +34173,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $931万
@@ -34332,7 +34196,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1363万
@@ -34356,15 +34220,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $920万
@@ -34379,7 +34243,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1296万
@@ -34403,15 +34267,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $915万
@@ -34426,7 +34290,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1233万
@@ -34442,7 +34306,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34453,12 +34317,12 @@
       <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$1690万
+$25,000/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $830万
@@ -34473,7 +34337,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1230万
@@ -34489,7 +34353,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34500,12 +34364,12 @@
       <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$1683万
+$24,901/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $825万
@@ -34520,7 +34384,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1226万
@@ -34539,20 +34403,20 @@
       <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1415万
+$25,313/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$1676万
+$24,800/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $820万
@@ -34567,7 +34431,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1222万
@@ -34586,20 +34450,20 @@
       <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1409万
+$25,200/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+$1670万
+$24,701/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $816万
@@ -34614,7 +34478,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1335万
@@ -34633,20 +34497,20 @@
       <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1398万
+$25,000/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$1663万
+$24,600/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $811万
@@ -34661,7 +34525,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1215万
@@ -34677,7 +34541,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34688,12 +34552,12 @@
       <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$1616万
+$23,901/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $806万
@@ -34708,7 +34572,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1331万
@@ -34724,7 +34588,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34735,12 +34599,12 @@
       <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$1614万
+$23,880/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $806万
@@ -34755,7 +34619,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1194万
@@ -34774,20 +34638,20 @@
       <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1342万
+$24,000/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+$1678万
+$24,830/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $796万
@@ -34802,7 +34666,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1185万
@@ -34821,12 +34685,106 @@
       <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
+$1348万
+$24,158/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
+$1600万
+$23,529/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 422呎 (2房)
+$861万
+$20,410/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 657呎 (3房)
+$1183万
+$18,003/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$983万
+$21,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
+$1436万
+$25,738/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
+$1564万
+$23,000/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 422呎 (2房)
+$844万
+$20,002/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 657呎 (3房)
+$1308万
+$19,915/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$981万
+$21,902/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34834,38 +34792,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$861万
-$20,410/呎
+$842万
+$19,943/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1183万
-$18,003/呎
+$1306万
+$19,875/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$983万
-$21,946/呎
+$979万
+$21,857/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34873,7 +34831,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34881,38 +34839,179 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$844万
-$20,002/呎
+$766万
+$18,152/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1308万
-$19,915/呎
+$1246万
+$18,973/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$981万
-$21,902/呎
+$977万
+$21,815/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 422呎 (2房)
+$764万
+$18,100/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 657呎 (3房)
+$1301万
+$19,796/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$975万
+$21,770/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 422呎 (2房)
+$762万
+$18,045/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 657呎 (3房)
+$1301万
+$19,796/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$975万
+$21,770/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 558呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 680呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 422呎 (2房)
+$762万
+$18,045/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 657呎 (3房)
+$1169万
+$17,788/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$971万
+$21,683/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -34920,7 +35019,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -34928,38 +35027,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$842万
-$19,943/呎
+$748万
+$17,723/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1306万
-$19,875/呎
+$1293万
+$19,676/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$979万
-$21,857/呎
+$970万
+$21,641/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -34967,7 +35066,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -34975,38 +35074,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$766万
-$18,152/呎
+$818万
+$19,372/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1246万
-$18,973/呎
+$1178万
+$17,930/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$977万
-$21,815/呎
+$968万
+$21,596/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35014,7 +35113,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35022,38 +35121,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$764万
-$18,100/呎
+$815万
+$19,313/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1301万
-$19,796/呎
+$1176万
+$17,893/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$975万
-$21,770/呎
+$966万
+$21,554/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35061,7 +35160,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35069,38 +35168,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$762万
-$18,045/呎
+$820万
+$19,429/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1301万
-$19,796/呎
+$1159万
+$17,645/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$975万
-$21,770/呎
+$964万
+$21,511/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35108,7 +35207,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35116,38 +35215,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$762万
-$18,045/呎
+$814万
+$19,294/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1169万
-$17,788/呎
+$1282万
+$19,519/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$971万
-$21,683/呎
+$962万
+$21,467/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35155,7 +35254,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35163,38 +35262,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$748万
-$17,723/呎
+$802万
+$19,002/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1293万
-$19,676/呎
+$1169万
+$17,787/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$970万
-$21,641/呎
+$960万
+$21,424/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35202,7 +35301,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35210,38 +35309,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$818万
-$19,372/呎
+$705万
+$16,716/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1178万
-$17,930/呎
+$1280万
+$19,481/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$968万
-$21,596/呎
+$960万
+$21,424/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35249,7 +35348,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35257,38 +35356,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$815万
-$19,313/呎
+$782万
+$18,528/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1176万
-$17,893/呎
+$1164万
+$17,717/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$966万
-$21,554/呎
+$956万
+$21,339/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35296,7 +35395,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35304,38 +35403,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$820万
-$19,429/呎
+$710万
+$16,815/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1159万
-$17,645/呎
+$1272万
+$19,364/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$964万
-$21,511/呎
+$954万
+$21,297/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35343,7 +35442,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35351,38 +35450,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$814万
-$19,294/呎
+$733万
+$17,365/呎
 (26年-08月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
-$1282万
-$19,519/呎
+$1188万
+$18,088/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$962万
-$21,467/呎
+$951万
+$21,221/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 -
@@ -35390,7 +35489,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 -
@@ -35398,242 +35497,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
-        <is>
-          <t>E | 422呎 (2房)
-$802万
-$19,002/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>A | 657呎 (3房)
-$1169万
-$17,787/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$960万
-$21,424/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>E | 422呎 (2房)
-$705万
-$16,716/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>A | 657呎 (3房)
-$1280万
-$19,481/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$960万
-$21,424/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>E | 422呎 (2房)
-$782万
-$18,528/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>A | 657呎 (3房)
-$1164万
-$17,717/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$956万
-$21,339/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>E | 422呎 (2房)
-$710万
-$16,815/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>A | 657呎 (3房)
-$1272万
-$19,364/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$954万
-$21,297/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="inlineStr">
-        <is>
-          <t>E | 422呎 (2房)
-$733万
-$17,365/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>A | 657呎 (3房)
-$1188万
-$18,088/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$951万
-$21,221/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>D | 680呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $770万
@@ -35651,33 +35515,33 @@
       <c r="B43" s="23" t="inlineStr">
         <is>
           <t>A | 619呎 (3房)
+$1486万
+$24,000/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>B | 410呎 (2房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>B | 410呎 (2房)
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>C | 521呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>D | 643呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>C | 521呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>D | 643呎 (3房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -35765,27 +35629,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -35913,12 +35777,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -35984,12 +35848,12 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -36055,12 +35919,12 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -36087,7 +35951,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $783万
@@ -36095,7 +35959,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $942万
@@ -36126,12 +35990,12 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -36158,7 +36022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $781万
@@ -36166,7 +36030,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $955万
@@ -36197,12 +36061,12 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -36229,7 +36093,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $853万
@@ -36237,7 +36101,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $924万
@@ -36268,12 +36132,12 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -36300,7 +36164,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $850万
@@ -36308,7 +36172,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $1002万
@@ -36339,12 +36203,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -36355,7 +36219,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $598万
@@ -36371,7 +36235,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $848万
@@ -36379,7 +36243,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $992万
@@ -36410,12 +36274,12 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -36426,7 +36290,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $596万
@@ -36442,7 +36306,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $845万
@@ -36450,7 +36314,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $982万
@@ -36481,12 +36345,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -36497,7 +36361,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $596万
@@ -36513,7 +36377,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $845万
@@ -36521,7 +36385,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $982万
@@ -36552,12 +36416,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -36568,7 +36432,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $607万
@@ -36584,7 +36448,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $767万
@@ -36592,7 +36456,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $970万
@@ -36623,12 +36487,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -36639,7 +36503,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $646万
@@ -36655,7 +36519,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $837万
@@ -36663,7 +36527,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $965万
@@ -36694,12 +36558,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -36710,7 +36574,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $617万
@@ -36726,7 +36590,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $762万
@@ -36734,7 +36598,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $959万
@@ -36781,7 +36645,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $587万
@@ -36797,7 +36661,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $760万
@@ -36805,7 +36669,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $870万
@@ -36852,7 +36716,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $585万
@@ -36868,7 +36732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $758万
@@ -36876,7 +36740,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $865万
@@ -36923,7 +36787,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $639万
@@ -36939,7 +36803,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $756万
@@ -36947,7 +36811,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $860万
@@ -36994,7 +36858,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $609万
@@ -37010,7 +36874,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $753万
@@ -37018,7 +36882,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $896万
@@ -37065,7 +36929,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $580万
@@ -37081,7 +36945,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $751万
@@ -37089,7 +36953,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $851万
@@ -37136,7 +37000,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $580万
@@ -37152,7 +37016,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $769万
@@ -37160,7 +37024,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $851万
@@ -37207,7 +37071,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $590万
@@ -37223,7 +37087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $818万
@@ -37231,7 +37095,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $841万
@@ -37294,7 +37158,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $746万
@@ -37302,7 +37166,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $829万
@@ -37318,7 +37182,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $889万
@@ -37365,7 +37229,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $745万
@@ -37373,7 +37237,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $812万
@@ -37389,7 +37253,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $871万
@@ -37436,7 +37300,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $814万
@@ -37444,7 +37308,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $887万
@@ -37460,7 +37324,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $858万
@@ -37491,7 +37355,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $588万
@@ -37507,7 +37371,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $812万
@@ -37515,7 +37379,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $884万
@@ -37531,7 +37395,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $948万
@@ -37562,7 +37426,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $560万
@@ -37578,7 +37442,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $740万
@@ -37586,7 +37450,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $843万
@@ -37602,7 +37466,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $945万
@@ -37633,7 +37497,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $612万
@@ -37649,7 +37513,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $739万
@@ -37657,7 +37521,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $879万
@@ -37673,7 +37537,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $942万
@@ -37720,7 +37584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $739万
@@ -37728,7 +37592,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $802万
@@ -37744,7 +37608,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $850万
@@ -37791,7 +37655,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $806万
@@ -37799,7 +37663,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $874万
@@ -37815,7 +37679,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $845万
@@ -37862,7 +37726,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $734万
@@ -37870,7 +37734,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $795万
@@ -37886,7 +37750,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $843万
@@ -37917,7 +37781,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $545万
@@ -37933,7 +37797,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $733万
@@ -37941,7 +37805,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $868万
@@ -37957,7 +37821,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $931万
@@ -37988,7 +37852,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $550万
@@ -38004,7 +37868,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $801万
@@ -38012,7 +37876,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $789万
@@ -38028,7 +37892,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $916万
@@ -38059,7 +37923,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $548万
@@ -38075,7 +37939,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $799万
@@ -38083,7 +37947,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $783万
@@ -38099,7 +37963,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $840万
@@ -38146,7 +38010,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $728万
@@ -38154,7 +38018,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $772万
@@ -38170,7 +38034,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $818万
@@ -38217,7 +38081,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $796万
@@ -38225,7 +38089,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $743万
@@ -38241,7 +38105,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $875万
@@ -38288,7 +38152,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $796万
@@ -38296,7 +38160,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $752万
@@ -38312,7 +38176,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I39" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $827万
@@ -38343,7 +38207,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $542万
@@ -38359,7 +38223,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $793万
@@ -38367,7 +38231,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $819万
@@ -38383,7 +38247,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I40" s="22" t="inlineStr">
+      <c r="I40" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $802万
@@ -38414,7 +38278,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $549万
@@ -38430,7 +38294,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $785万
@@ -38438,7 +38302,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $737万
@@ -38454,7 +38318,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="I41" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $800万
@@ -38485,7 +38349,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $580万
@@ -38501,7 +38365,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $699万
@@ -38509,7 +38373,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $776万
@@ -38525,7 +38389,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="23" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $795万
@@ -38596,12 +38460,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I43" s="20" t="inlineStr">
+      <c r="I43" s="22" t="inlineStr">
         <is>
           <t>H | 437呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,11 +122,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -207,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -269,13 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1117,7 +1109,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1319,7 +1311,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1451,7 +1443,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1653,7 +1645,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1987,7 +1979,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2313,7 +2305,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2639,7 +2631,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2965,7 +2957,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3291,7 +3283,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3617,7 +3609,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3943,7 +3935,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4269,7 +4261,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4595,7 +4587,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4913,7 +4905,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5231,7 +5223,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -5541,7 +5533,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5851,7 +5843,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6161,7 +6153,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6479,7 +6471,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6797,7 +6789,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7107,7 +7099,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7417,7 +7409,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7727,7 +7719,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8053,7 +8045,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -8379,7 +8371,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8705,7 +8697,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9031,7 +9023,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9357,7 +9349,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9683,7 +9675,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10009,7 +10001,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10335,7 +10327,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10661,7 +10653,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -10987,7 +10979,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11313,7 +11305,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11639,7 +11631,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -11965,7 +11957,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12291,7 +12283,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12617,7 +12609,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12943,7 +12935,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -13969,7 +13961,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14101,7 +14093,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -14163,7 +14155,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14295,7 +14287,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14357,7 +14349,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14489,7 +14481,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14621,7 +14613,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14683,7 +14675,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -14815,7 +14807,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -14877,7 +14869,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15009,7 +15001,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15335,7 +15327,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15397,7 +15389,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -15529,7 +15521,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15855,7 +15847,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -15917,7 +15909,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16049,7 +16041,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16375,7 +16367,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16437,7 +16429,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16569,7 +16561,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16895,7 +16887,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16957,7 +16949,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -17089,7 +17081,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17477,7 +17469,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17609,7 +17601,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17997,7 +17989,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -18129,7 +18121,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -18517,7 +18509,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -18649,7 +18641,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -19037,7 +19029,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19169,7 +19161,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -19557,7 +19549,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -19689,7 +19681,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -20077,7 +20069,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -20209,7 +20201,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -20597,7 +20589,7 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -20659,7 +20651,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -20721,7 +20713,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -21109,7 +21101,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -21171,7 +21163,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -21233,7 +21225,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -21621,7 +21613,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -21683,7 +21675,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -21745,7 +21737,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -22133,7 +22125,7 @@
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -22195,7 +22187,7 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -22257,7 +22249,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -22645,7 +22637,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -22707,7 +22699,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -23235,7 +23227,7 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -23297,7 +23289,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -23685,7 +23677,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -23747,7 +23739,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -24135,7 +24127,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -24267,7 +24259,7 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -24655,7 +24647,7 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -24787,7 +24779,7 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -25175,7 +25167,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -25237,7 +25229,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -25299,7 +25291,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -25749,7 +25741,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -25811,7 +25803,7 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
@@ -26261,7 +26253,7 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -26323,7 +26315,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -26773,7 +26765,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -26835,7 +26827,7 @@
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -27223,7 +27215,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -27355,7 +27347,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -27743,7 +27735,7 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
@@ -27805,7 +27797,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -27867,7 +27859,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -28255,7 +28247,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -28317,7 +28309,7 @@
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
@@ -28379,7 +28371,7 @@
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -28829,7 +28821,7 @@
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -28891,7 +28883,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -29341,7 +29333,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -29403,7 +29395,7 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -29853,7 +29845,7 @@
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
@@ -29915,7 +29907,7 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -30303,7 +30295,7 @@
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -30435,7 +30427,7 @@
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -30823,7 +30815,7 @@
       </c>
       <c r="F467" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -30885,7 +30877,7 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -30947,7 +30939,7 @@
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -31335,7 +31327,7 @@
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
@@ -31397,7 +31389,7 @@
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
@@ -31459,7 +31451,7 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -31909,7 +31901,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -31971,7 +31963,7 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -32421,7 +32413,7 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -32483,7 +32475,7 @@
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G493" s="3" t="inlineStr">
@@ -32933,7 +32925,7 @@
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -32995,7 +32987,7 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
@@ -33664,12 +33656,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -33786,7 +33778,7 @@
           <t>B | 444呎 (2房)
 $1122万
 $25,270/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -33797,7 +33789,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33810,7 +33802,7 @@
           <t>E | 423呎 (2房)
 $1124万
 $26,577/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33833,7 +33825,7 @@
           <t>B | 444呎 (2房)
 $1109万
 $24,971/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -33844,7 +33836,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33857,7 +33849,7 @@
           <t>E | 423呎 (2房)
 $1098万
 $25,955/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33867,7 +33859,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1450万
@@ -33880,7 +33872,7 @@
           <t>B | 444呎 (2房)
 $1081万
 $24,338/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -33891,7 +33883,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33899,7 +33891,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $979万
@@ -33914,7 +33906,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1435万
@@ -33927,7 +33919,7 @@
           <t>B | 444呎 (2房)
 $1070万
 $24,097/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -33938,7 +33930,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33946,7 +33938,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $969万
@@ -33961,7 +33953,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1297万
@@ -33974,7 +33966,7 @@
           <t>B | 444呎 (2房)
 $1059万
 $23,858/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -33985,7 +33977,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33993,7 +33985,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $960万
@@ -34008,7 +34000,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1407万
@@ -34021,7 +34013,7 @@
           <t>B | 444呎 (2房)
 $1049万
 $23,624/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -34032,7 +34024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34040,7 +34032,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $950万
@@ -34055,7 +34047,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1393万
@@ -34068,7 +34060,7 @@
           <t>B | 444呎 (2房)
 $1038万
 $23,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -34079,7 +34071,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34087,7 +34079,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $859万
@@ -34102,7 +34094,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1259万
@@ -34115,7 +34107,7 @@
           <t>B | 444呎 (2房)
 $1028万
 $23,158/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -34126,7 +34118,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34134,7 +34126,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $931万
@@ -34149,7 +34141,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1371万
@@ -34162,7 +34154,7 @@
           <t>B | 444呎 (2房)
 $1022万
 $23,020/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -34173,7 +34165,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34181,7 +34173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $931万
@@ -34196,7 +34188,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1363万
@@ -34209,7 +34201,7 @@
           <t>B | 444呎 (2房)
 $1016万
 $22,883/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -34220,7 +34212,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34228,7 +34220,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $920万
@@ -34243,7 +34235,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1296万
@@ -34256,7 +34248,7 @@
           <t>B | 444呎 (2房)
 $1010万
 $22,750/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -34267,7 +34259,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -34275,7 +34267,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $915万
@@ -34290,7 +34282,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1233万
@@ -34303,10 +34295,10 @@
           <t>B | 444呎 (2房)
 $1007万
 $22,682/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34314,7 +34306,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1690万
@@ -34322,7 +34314,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $830万
@@ -34337,7 +34329,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1230万
@@ -34350,10 +34342,10 @@
           <t>B | 444呎 (2房)
 $1004万
 $22,615/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34361,7 +34353,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1683万
@@ -34369,7 +34361,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $825万
@@ -34384,7 +34376,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1226万
@@ -34397,10 +34389,10 @@
           <t>B | 444呎 (2房)
 $1001万
 $22,547/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 $1415万
@@ -34408,7 +34400,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1676万
@@ -34416,7 +34408,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $820万
@@ -34431,7 +34423,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1222万
@@ -34444,10 +34436,10 @@
           <t>B | 444呎 (2房)
 $998万
 $22,480/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 $1409万
@@ -34455,7 +34447,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1670万
@@ -34463,7 +34455,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $816万
@@ -34478,7 +34470,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1335万
@@ -34491,10 +34483,10 @@
           <t>B | 444呎 (2房)
 $995万
 $22,412/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 $1398万
@@ -34502,7 +34494,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1663万
@@ -34510,7 +34502,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $811万
@@ -34525,7 +34517,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1215万
@@ -34538,10 +34530,10 @@
           <t>B | 444呎 (2房)
 $992万
 $22,345/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34549,7 +34541,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1616万
@@ -34557,7 +34549,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $806万
@@ -34572,7 +34564,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1331万
@@ -34585,10 +34577,10 @@
           <t>B | 444呎 (2房)
 $992万
 $22,345/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -34596,7 +34588,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1614万
@@ -34604,7 +34596,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $806万
@@ -34619,7 +34611,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
 $1194万
@@ -34632,10 +34624,10 @@
           <t>B | 444呎 (2房)
 $986万
 $22,212/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 $1342万
@@ -34643,7 +34635,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 $1678万
@@ -34651,7 +34643,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $796万
@@ -34666,7 +34658,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1185万
@@ -34679,10 +34671,10 @@
           <t>B | 448呎 (2房)
 $985万
 $21,989/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1348万
@@ -34690,7 +34682,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1600万
@@ -34698,7 +34690,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $861万
@@ -34713,7 +34705,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1183万
@@ -34726,10 +34718,10 @@
           <t>B | 448呎 (2房)
 $983万
 $21,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1436万
@@ -34737,7 +34729,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1564万
@@ -34745,7 +34737,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $844万
@@ -34760,7 +34752,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1308万
@@ -34773,10 +34765,10 @@
           <t>B | 448呎 (2房)
 $981万
 $21,902/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34784,7 +34776,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34792,7 +34784,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $842万
@@ -34807,7 +34799,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1306万
@@ -34820,10 +34812,10 @@
           <t>B | 448呎 (2房)
 $979万
 $21,857/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34831,7 +34823,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34839,7 +34831,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $766万
@@ -34854,7 +34846,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1246万
@@ -34867,10 +34859,10 @@
           <t>B | 448呎 (2房)
 $977万
 $21,815/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34878,7 +34870,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34886,7 +34878,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $764万
@@ -34901,7 +34893,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1301万
@@ -34914,10 +34906,10 @@
           <t>B | 448呎 (2房)
 $975万
 $21,770/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34925,7 +34917,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34933,7 +34925,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $762万
@@ -34948,7 +34940,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1301万
@@ -34961,10 +34953,10 @@
           <t>B | 448呎 (2房)
 $975万
 $21,770/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 招标单位
@@ -34972,7 +34964,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 招标单位
@@ -34980,7 +34972,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $762万
@@ -34995,7 +34987,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1169万
@@ -35008,7 +35000,7 @@
           <t>B | 448呎 (2房)
 $971万
 $21,683/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -35027,7 +35019,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $748万
@@ -35042,7 +35034,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1293万
@@ -35055,7 +35047,7 @@
           <t>B | 448呎 (2房)
 $970万
 $21,641/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -35074,7 +35066,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $818万
@@ -35089,7 +35081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1178万
@@ -35102,7 +35094,7 @@
           <t>B | 448呎 (2房)
 $968万
 $21,596/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -35121,7 +35113,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $815万
@@ -35136,7 +35128,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1176万
@@ -35149,7 +35141,7 @@
           <t>B | 448呎 (2房)
 $966万
 $21,554/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -35168,7 +35160,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $820万
@@ -35183,7 +35175,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1159万
@@ -35196,7 +35188,7 @@
           <t>B | 448呎 (2房)
 $964万
 $21,511/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -35215,7 +35207,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $814万
@@ -35230,7 +35222,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1282万
@@ -35243,7 +35235,7 @@
           <t>B | 448呎 (2房)
 $962万
 $21,467/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -35262,7 +35254,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $802万
@@ -35277,7 +35269,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1169万
@@ -35290,7 +35282,7 @@
           <t>B | 448呎 (2房)
 $960万
 $21,424/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -35309,7 +35301,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $705万
@@ -35324,7 +35316,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1280万
@@ -35337,7 +35329,7 @@
           <t>B | 448呎 (2房)
 $960万
 $21,424/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -35356,7 +35348,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $782万
@@ -35371,7 +35363,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1164万
@@ -35384,7 +35376,7 @@
           <t>B | 448呎 (2房)
 $956万
 $21,339/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -35403,7 +35395,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $710万
@@ -35418,7 +35410,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1272万
@@ -35431,7 +35423,7 @@
           <t>B | 448呎 (2房)
 $954万
 $21,297/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -35450,7 +35442,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $733万
@@ -35465,7 +35457,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>A | 657呎 (3房)
 $1188万
@@ -35478,7 +35470,7 @@
           <t>B | 448呎 (2房)
 $951万
 $21,221/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -35497,7 +35489,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $770万
@@ -35512,7 +35504,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>A | 619呎 (3房)
 $1486万
@@ -35520,7 +35512,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>B | 410呎 (2房)
 招标单位
@@ -35528,7 +35520,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D43" s="21" t="inlineStr">
         <is>
           <t>C | 521呎 (3房)
 招标单位
@@ -35536,7 +35528,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E43" s="21" t="inlineStr">
         <is>
           <t>D | 643呎 (3房)
 招标单位
@@ -35629,12 +35621,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -35777,7 +35769,7 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -35790,7 +35782,7 @@
           <t>B | 313呎 (1房)
 $782万
 $24,997/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35798,7 +35790,7 @@
           <t>C | 306呎 (1房)
 $769万
 $25,131/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -35814,7 +35806,7 @@
           <t>E | 418呎 (2房)
 $1023万
 $24,469/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -35822,7 +35814,7 @@
           <t>F | 450呎 (2房)
 $1186万
 $26,347/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -35838,7 +35830,7 @@
           <t>H | 473呎 (2房)
 $1260万
 $26,630/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -35848,7 +35840,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -35861,7 +35853,7 @@
           <t>B | 313呎 (1房)
 $773万
 $24,700/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35869,7 +35861,7 @@
           <t>C | 306呎 (1房)
 $760万
 $24,833/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -35885,7 +35877,7 @@
           <t>E | 418呎 (2房)
 $988万
 $23,641/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -35893,7 +35885,7 @@
           <t>F | 450呎 (2房)
 $1158万
 $25,729/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -35909,7 +35901,7 @@
           <t>H | 473呎 (2房)
 $1230万
 $26,006/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -35919,7 +35911,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -35932,7 +35924,7 @@
           <t>B | 313呎 (1房)
 $754万
 $24,073/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35940,7 +35932,7 @@
           <t>C | 306呎 (1房)
 $741万
 $24,203/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -35951,7 +35943,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $783万
@@ -35959,7 +35951,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $942万
@@ -35980,7 +35972,7 @@
           <t>H | 473呎 (2房)
 $1192万
 $25,199/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -35990,7 +35982,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36003,7 +35995,7 @@
           <t>B | 313呎 (1房)
 $746万
 $23,837/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -36011,7 +36003,7 @@
           <t>C | 306呎 (1房)
 $733万
 $23,964/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -36022,7 +36014,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $781万
@@ -36030,7 +36022,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $955万
@@ -36051,7 +36043,7 @@
           <t>H | 473呎 (2房)
 $1180万
 $24,949/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36061,7 +36053,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36074,7 +36066,7 @@
           <t>B | 313呎 (1房)
 $739万
 $23,601/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -36082,7 +36074,7 @@
           <t>C | 306呎 (1房)
 $726万
 $23,725/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -36093,7 +36085,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $853万
@@ -36101,7 +36093,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $924万
@@ -36122,7 +36114,7 @@
           <t>H | 473呎 (2房)
 $1168万
 $24,702/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36132,7 +36124,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36145,7 +36137,7 @@
           <t>B | 313呎 (1房)
 $731万
 $23,367/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -36153,7 +36145,7 @@
           <t>C | 306呎 (1房)
 $719万
 $23,490/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -36164,7 +36156,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $850万
@@ -36172,7 +36164,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $1002万
@@ -36193,7 +36185,7 @@
           <t>H | 473呎 (2房)
 $1157万
 $24,459/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36203,7 +36195,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36216,10 +36208,10 @@
           <t>B | 313呎 (1房)
 $724万
 $23,134/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $598万
@@ -36235,7 +36227,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $848万
@@ -36243,7 +36235,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $992万
@@ -36264,7 +36256,7 @@
           <t>H | 473呎 (2房)
 $1145万
 $24,216/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36274,7 +36266,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36287,10 +36279,10 @@
           <t>B | 313呎 (1房)
 $722万
 $23,064/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $596万
@@ -36306,7 +36298,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $845万
@@ -36314,7 +36306,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $982万
@@ -36335,7 +36327,7 @@
           <t>H | 473呎 (2房)
 $1134万
 $23,977/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36345,7 +36337,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36358,10 +36350,10 @@
           <t>B | 313呎 (1房)
 $722万
 $23,064/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $596万
@@ -36377,7 +36369,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $845万
@@ -36385,7 +36377,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $982万
@@ -36406,7 +36398,7 @@
           <t>H | 473呎 (2房)
 $1134万
 $23,977/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36416,7 +36408,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36429,10 +36421,10 @@
           <t>B | 313呎 (1房)
 $718万
 $22,927/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $607万
@@ -36448,7 +36440,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $767万
@@ -36456,7 +36448,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $970万
@@ -36477,7 +36469,7 @@
           <t>H | 473呎 (2房)
 $1121万
 $23,691/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36487,7 +36479,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36500,10 +36492,10 @@
           <t>B | 313呎 (1房)
 $715万
 $22,840/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $646万
@@ -36519,7 +36511,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $837万
@@ -36527,7 +36519,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $965万
@@ -36548,7 +36540,7 @@
           <t>H | 473呎 (2房)
 $1114万
 $23,550/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36558,7 +36550,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
 招标单位
@@ -36571,10 +36563,10 @@
           <t>B | 313呎 (1房)
 $713万
 $22,773/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $617万
@@ -36590,7 +36582,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $762万
@@ -36598,7 +36590,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $959万
@@ -36619,7 +36611,7 @@
           <t>H | 473呎 (2房)
 $1107万
 $23,410/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36634,7 +36626,7 @@
           <t>A | 672呎 (3房)
 $1593万
 $23,699/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -36642,10 +36634,10 @@
           <t>B | 313呎 (1房)
 $711万
 $22,706/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $587万
@@ -36661,7 +36653,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $760万
@@ -36669,7 +36661,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $870万
@@ -36690,7 +36682,7 @@
           <t>H | 473呎 (2房)
 $1101万
 $23,271/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36697,7 @@
           <t>A | 672呎 (3房)
 $1588万
 $23,629/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -36713,10 +36705,10 @@
           <t>B | 313呎 (1房)
 $708万
 $22,636/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $585万
@@ -36732,7 +36724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $758万
@@ -36740,7 +36732,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $865万
@@ -36761,7 +36753,7 @@
           <t>H | 473呎 (2房)
 $1094万
 $23,131/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36776,7 +36768,7 @@
           <t>A | 672呎 (3房)
 $1583万
 $23,558/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -36784,10 +36776,10 @@
           <t>B | 313呎 (1房)
 $706万
 $22,569/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $639万
@@ -36803,7 +36795,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $756万
@@ -36811,7 +36803,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $860万
@@ -36832,7 +36824,7 @@
           <t>H | 473呎 (2房)
 $1088万
 $22,994/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36847,7 +36839,7 @@
           <t>A | 672呎 (3房)
 $1578万
 $23,488/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -36855,10 +36847,10 @@
           <t>B | 313呎 (1房)
 $704万
 $22,502/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $609万
@@ -36874,7 +36866,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $753万
@@ -36882,7 +36874,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $896万
@@ -36903,7 +36895,7 @@
           <t>H | 473呎 (2房)
 $1081万
 $22,856/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36918,7 +36910,7 @@
           <t>A | 672呎 (3房)
 $1574万
 $23,418/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -36926,10 +36918,10 @@
           <t>B | 313呎 (1房)
 $702万
 $22,435/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $580万
@@ -36945,7 +36937,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $751万
@@ -36953,7 +36945,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $851万
@@ -36974,7 +36966,7 @@
           <t>H | 473呎 (2房)
 $1075万
 $22,721/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36989,7 +36981,7 @@
           <t>A | 672呎 (3房)
 $1574万
 $23,418/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -37000,7 +36992,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $580万
@@ -37016,7 +37008,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $769万
@@ -37024,7 +37016,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $851万
@@ -37060,7 +37052,7 @@
           <t>A | 672呎 (3房)
 $1564万
 $23,278/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -37068,10 +37060,10 @@
           <t>B | 313呎 (1房)
 $698万
 $22,300/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
 $590万
@@ -37087,7 +37079,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 418呎 (2房)
 $818万
@@ -37095,7 +37087,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $841万
@@ -37116,7 +37108,7 @@
           <t>H | 473呎 (2房)
 $1062万
 $22,450/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -37131,7 +37123,7 @@
           <t>A | 672呎 (3房)
 $1549万
 $23,045/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -37147,7 +37139,7 @@
           <t>C | 304呎 (1房)
 $680万
 $22,352/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -37158,7 +37150,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $746万
@@ -37166,7 +37158,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $829万
@@ -37182,7 +37174,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $889万
@@ -37202,7 +37194,7 @@
           <t>A | 672呎 (3房)
 $1542万
 $22,952/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -37218,7 +37210,7 @@
           <t>C | 304呎 (1房)
 $678万
 $22,286/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -37229,7 +37221,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $745万
@@ -37237,7 +37229,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $812万
@@ -37253,7 +37245,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $871万
@@ -37273,7 +37265,7 @@
           <t>A | 672呎 (3房)
 $1536万
 $22,862/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -37281,7 +37273,7 @@
           <t>B | 313呎 (1房)
 $687万
 $21,946/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37289,7 +37281,7 @@
           <t>C | 304呎 (1房)
 $676万
 $22,220/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -37300,7 +37292,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $814万
@@ -37308,7 +37300,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $887万
@@ -37324,7 +37316,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $858万
@@ -37344,7 +37336,7 @@
           <t>A | 672呎 (3房)
 $1530万
 $22,769/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -37352,10 +37344,10 @@
           <t>B | 313呎 (1房)
 $685万
 $21,879/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $588万
@@ -37371,7 +37363,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $812万
@@ -37379,7 +37371,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $884万
@@ -37395,7 +37387,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $948万
@@ -37415,7 +37407,7 @@
           <t>A | 672呎 (3房)
 $1524万
 $22,679/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -37423,10 +37415,10 @@
           <t>B | 313呎 (1房)
 $683万
 $21,815/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $560万
@@ -37442,7 +37434,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $740万
@@ -37450,7 +37442,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $843万
@@ -37466,7 +37458,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $945万
@@ -37486,7 +37478,7 @@
           <t>A | 672呎 (3房)
 $1518万
 $22,588/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -37494,10 +37486,10 @@
           <t>B | 313呎 (1房)
 $681万
 $21,748/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $612万
@@ -37513,7 +37505,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $739万
@@ -37521,7 +37513,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $879万
@@ -37537,7 +37529,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $942万
@@ -37557,7 +37549,7 @@
           <t>A | 672呎 (3房)
 $1518万
 $22,588/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -37573,7 +37565,7 @@
           <t>C | 304呎 (1房)
 $665万
 $21,865/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -37584,7 +37576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $739万
@@ -37592,7 +37584,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $802万
@@ -37608,7 +37600,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I31" s="23" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $850万
@@ -37628,7 +37620,7 @@
           <t>A | 672呎 (3房)
 $1506万
 $22,408/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -37636,7 +37628,7 @@
           <t>B | 313呎 (1房)
 $677万
 $21,617/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -37644,7 +37636,7 @@
           <t>C | 304呎 (1房)
 $661万
 $21,734/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -37655,7 +37647,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $806万
@@ -37663,7 +37655,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $874万
@@ -37679,7 +37671,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $845万
@@ -37699,7 +37691,7 @@
           <t>A | 672呎 (3房)
 $1500万
 $22,317/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -37707,7 +37699,7 @@
           <t>B | 313呎 (1房)
 $675万
 $21,553/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -37715,7 +37707,7 @@
           <t>C | 304呎 (1房)
 $659万
 $21,668/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -37726,7 +37718,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $734万
@@ -37734,7 +37726,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $795万
@@ -37750,7 +37742,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I33" s="23" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $843万
@@ -37770,7 +37762,7 @@
           <t>A | 672呎 (3房)
 $1494万
 $22,228/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -37778,10 +37770,10 @@
           <t>B | 313呎 (1房)
 $673万
 $21,489/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $545万
@@ -37797,7 +37789,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $733万
@@ -37805,7 +37797,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $868万
@@ -37821,7 +37813,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $931万
@@ -37841,7 +37833,7 @@
           <t>A | 672呎 (3房)
 $1488万
 $22,140/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -37849,10 +37841,10 @@
           <t>B | 313呎 (1房)
 $671万
 $21,425/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $550万
@@ -37868,7 +37860,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $801万
@@ -37876,7 +37868,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $789万
@@ -37892,7 +37884,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I35" s="23" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $916万
@@ -37912,7 +37904,7 @@
           <t>A | 672呎 (3房)
 $1482万
 $22,051/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -37920,10 +37912,10 @@
           <t>B | 313呎 (1房)
 $669万
 $21,361/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $548万
@@ -37939,7 +37931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $799万
@@ -37947,7 +37939,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $783万
@@ -37963,7 +37955,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I36" s="23" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $840万
@@ -37983,7 +37975,7 @@
           <t>A | 672呎 (3房)
 $1476万
 $21,963/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -37999,7 +37991,7 @@
           <t>C | 304呎 (1房)
 $652万
 $21,431/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -38010,7 +38002,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $728万
@@ -38018,7 +38010,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G37" s="23" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $772万
@@ -38034,7 +38026,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I37" s="23" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $818万
@@ -38054,7 +38046,7 @@
           <t>A | 672呎 (3房)
 $1470万
 $21,875/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -38062,7 +38054,7 @@
           <t>B | 313呎 (1房)
 $664万
 $21,230/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -38070,7 +38062,7 @@
           <t>C | 304呎 (1房)
 $651万
 $21,411/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
@@ -38081,7 +38073,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $796万
@@ -38089,7 +38081,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $743万
@@ -38105,7 +38097,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I38" s="23" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $875万
@@ -38125,7 +38117,7 @@
           <t>A | 672呎 (3房)
 $1470万
 $21,875/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
@@ -38133,7 +38125,7 @@
           <t>B | 313呎 (1房)
 $664万
 $21,230/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -38141,7 +38133,7 @@
           <t>C | 304呎 (1房)
 $651万
 $21,411/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -38152,7 +38144,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $796万
@@ -38160,7 +38152,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $752万
@@ -38176,7 +38168,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I39" s="23" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $827万
@@ -38196,7 +38188,7 @@
           <t>A | 672呎 (3房)
 $1458万
 $21,699/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -38204,10 +38196,10 @@
           <t>B | 313呎 (1房)
 $661万
 $21,105/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $542万
@@ -38223,7 +38215,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $793万
@@ -38231,7 +38223,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $819万
@@ -38247,7 +38239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I40" s="23" t="inlineStr">
+      <c r="I40" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $802万
@@ -38267,7 +38259,7 @@
           <t>A | 672呎 (3房)
 $1452万
 $21,613/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
@@ -38275,10 +38267,10 @@
           <t>B | 313呎 (1房)
 $654万
 $20,895/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $549万
@@ -38294,7 +38286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $785万
@@ -38302,7 +38294,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $737万
@@ -38318,7 +38310,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I41" s="23" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $800万
@@ -38338,7 +38330,7 @@
           <t>A | 672呎 (3房)
 $1428万
 $21,246/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
@@ -38346,10 +38338,10 @@
           <t>B | 313呎 (1房)
 $642万
 $20,518/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
 $580万
@@ -38365,7 +38357,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
 $699万
@@ -38373,7 +38365,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr">
+      <c r="G42" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 $776万
@@ -38389,7 +38381,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I42" s="23" t="inlineStr">
+      <c r="I42" s="22" t="inlineStr">
         <is>
           <t>H | 476呎 (2房)
 $795万
@@ -38460,7 +38452,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="I43" s="21" t="inlineStr">
         <is>
           <t>H | 437呎 (2房)
 招标单位

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,11 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -202,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +273,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9605,7 +9613,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9613,34 +9621,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>14388000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>25785</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>12085920</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>21659</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -9869,34 +9869,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>16714000</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>24579</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>14039760</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>20647</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
@@ -9931,7 +9923,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -9939,34 +9931,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H145" s="5" t="n">
+        <v>14316000</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>25656</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>12025440</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>21551</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -10187,7 +10171,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10195,34 +10179,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H149" s="5" t="n">
+        <v>16631000</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>24457</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>13970040</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>20544</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -10257,7 +10233,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10265,34 +10241,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>14244000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>25527</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>11964960</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>21443</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -10513,7 +10481,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10521,34 +10489,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H154" s="5" t="n">
+        <v>16381000</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>24090</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>13760040</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>20235</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
@@ -10583,7 +10543,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10591,34 +10551,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H155" s="5" t="n">
+        <v>14030000</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>25143</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>11785200</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>21120</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -10839,7 +10791,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -10847,34 +10799,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H159" s="5" t="n">
+        <v>16217000</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>23849</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>13622280</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>20033</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N159" s="3" t="inlineStr">
@@ -10909,7 +10853,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -10917,34 +10861,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H160" s="5" t="n">
+        <v>13890000</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>24892</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>11667600</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>20910</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11165,7 +11101,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11173,34 +11109,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>16136000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>23729</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>13554240</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>19933</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -11235,7 +11163,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11243,34 +11171,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H165" s="5" t="n">
+        <v>13682000</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>24520</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>11492880</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>20597</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -11491,7 +11411,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11499,34 +11419,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>15814000</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>23256</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>13283760</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>19535</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11561,7 +11473,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -11569,34 +11481,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H170" s="5" t="n">
+        <v>13408000</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>24029</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>11262720</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>20184</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -11817,7 +11721,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11825,34 +11729,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H174" s="5" t="n">
+        <v>15814000</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>23256</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>13283760</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>19535</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -11887,7 +11783,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -11895,34 +11791,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>13408000</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>24029</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>11262720</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>20184</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
@@ -12143,7 +12031,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -12151,34 +12039,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I179" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H179" s="5" t="n">
+        <v>15655000</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>23022</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K179" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L179" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>13150200</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>19339</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -12213,7 +12093,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12221,34 +12101,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>13274000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>23789</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>11150160</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>19982</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12469,7 +12341,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -12477,34 +12349,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H184" s="5" t="n">
+        <v>15577000</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>22907</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>13084680</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>19242</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
@@ -12539,7 +12403,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12547,34 +12411,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H185" s="5" t="n">
+        <v>13208000</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>23670</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>11094720</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>19883</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -12795,7 +12651,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12803,34 +12659,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>15498000</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>22791</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>13018320</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>19145</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -12865,7 +12713,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -12873,34 +12721,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H190" s="5" t="n">
+        <v>13140000</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>23548</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>11037600</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>19781</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -14023,7 +13863,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14031,34 +13871,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H207" s="5" t="n">
+        <v>11063000</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>27115</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>9292920</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>22777</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14217,7 +14049,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14225,34 +14057,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H210" s="5" t="n">
+        <v>7967000</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>25951</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>6692280</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>21799</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14543,7 +14367,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14551,34 +14375,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>10803000</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>26478</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>9074520</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>22241</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14737,7 +14553,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14745,34 +14561,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>7872000</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>25642</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>6612480</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>21539</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -15063,7 +14871,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15071,34 +14879,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>10468000</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>25657</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>8793120</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>21552</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15257,7 +15057,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15265,34 +15065,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H226" s="5" t="n">
+        <v>7673000</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>24993</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>6445320</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>20995</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
@@ -15583,7 +15375,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15591,34 +15383,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H231" s="5" t="n">
+        <v>10365000</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>25404</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>8706600</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>21340</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15777,7 +15561,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15785,34 +15569,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H234" s="5" t="n">
+        <v>7597000</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>24746</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>6381480</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>20787</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -16103,7 +15879,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16111,34 +15887,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H239" s="5" t="n">
+        <v>10262000</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>25152</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>8620080</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>21128</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16297,7 +16065,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16305,34 +16073,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H242" s="5" t="n">
+        <v>7522000</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>24502</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>6318480</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>20581</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -16623,7 +16383,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16631,34 +16391,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H247" s="5" t="n">
+        <v>10161000</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>24904</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>8535240</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>20920</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
@@ -16817,7 +16569,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16825,34 +16577,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H250" s="5" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>24257</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>6255480</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>20376</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17143,7 +16887,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -17151,34 +16895,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H255" s="5" t="n">
+        <v>10060000</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>24657</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>8450400</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>20712</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
@@ -17337,7 +17073,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -17345,34 +17081,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H258" s="5" t="n">
+        <v>7374000</v>
+      </c>
+      <c r="I258" s="5" t="n">
+        <v>24020</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>6194160</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>20176</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -17663,7 +17391,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17671,34 +17399,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H263" s="5" t="n">
+        <v>9960000</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>24412</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>8366400</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>20506</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -17857,7 +17577,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17865,34 +17585,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H266" s="5" t="n">
+        <v>7352000</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>23948</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>6175680</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>20116</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -18183,7 +17895,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -18191,34 +17903,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H271" s="5" t="n">
+        <v>9960000</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>24412</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>8366400</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>20506</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
@@ -18377,7 +18081,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -18385,34 +18089,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H274" s="5" t="n">
+        <v>7352000</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>23948</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>6175680</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>20116</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
@@ -18703,7 +18399,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -18711,34 +18407,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H279" s="5" t="n">
+        <v>9842000</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>24123</v>
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>8267280</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>20263</v>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
@@ -18897,7 +18585,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -18905,34 +18593,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H282" s="5" t="n">
+        <v>7308000</v>
+      </c>
+      <c r="I282" s="5" t="n">
+        <v>23805</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>6138720</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>19996</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -19223,7 +18903,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19231,34 +18911,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H287" s="5" t="n">
+        <v>9784000</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>23980</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>8218560</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>20144</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -19417,7 +19089,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -19425,34 +19097,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H290" s="5" t="n">
+        <v>7280000</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>23713</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>6115200</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>19919</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
@@ -19743,7 +19407,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -19751,34 +19415,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H295" s="5" t="n">
+        <v>9725000</v>
+      </c>
+      <c r="I295" s="5" t="n">
+        <v>23836</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K295" s="5" t="n">
+        <v>8169000</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>20022</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -19937,7 +19593,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -19945,34 +19601,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H298" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H298" s="5" t="n">
+        <v>7258000</v>
+      </c>
+      <c r="I298" s="5" t="n">
+        <v>23642</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K298" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L298" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K298" s="5" t="n">
+        <v>6096720</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>19859</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N298" s="3" t="inlineStr">
@@ -20263,7 +19911,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -20271,34 +19919,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H303" s="5" t="n">
+        <v>9667000</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>23694</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>8120280</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>19903</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
@@ -20457,7 +20097,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -20465,34 +20105,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H306" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I306" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H306" s="5" t="n">
+        <v>7237000</v>
+      </c>
+      <c r="I306" s="5" t="n">
+        <v>23573</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K306" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L306" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K306" s="5" t="n">
+        <v>6079080</v>
+      </c>
+      <c r="L306" s="5" t="n">
+        <v>19802</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20775,7 +20407,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -20783,34 +20415,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H311" s="5" t="n">
+        <v>9610000</v>
+      </c>
+      <c r="I311" s="5" t="n">
+        <v>23554</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>8072400</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>19785</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N311" s="3" t="inlineStr">
@@ -20969,7 +20593,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -20977,34 +20601,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H314" s="5" t="n">
+        <v>7215000</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>23502</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>6060600</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>19741</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N314" s="3" t="inlineStr">
@@ -21287,7 +20903,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -21295,34 +20911,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H319" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I319" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H319" s="5" t="n">
+        <v>9552000</v>
+      </c>
+      <c r="I319" s="5" t="n">
+        <v>23412</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K319" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L319" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K319" s="5" t="n">
+        <v>8023680</v>
+      </c>
+      <c r="L319" s="5" t="n">
+        <v>19666</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N319" s="3" t="inlineStr">
@@ -21481,7 +21089,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -21489,34 +21097,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H322" s="5" t="n">
+        <v>7193000</v>
+      </c>
+      <c r="I322" s="5" t="n">
+        <v>23430</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K322" s="5" t="n">
+        <v>6042120</v>
+      </c>
+      <c r="L322" s="5" t="n">
+        <v>19681</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N322" s="3" t="inlineStr">
@@ -21799,7 +21399,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -21807,34 +21407,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H327" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I327" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H327" s="5" t="n">
+        <v>9495000</v>
+      </c>
+      <c r="I327" s="5" t="n">
+        <v>23272</v>
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K327" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L327" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K327" s="5" t="n">
+        <v>7975800</v>
+      </c>
+      <c r="L327" s="5" t="n">
+        <v>19549</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N327" s="3" t="inlineStr">
@@ -21993,7 +21585,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22001,34 +21593,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H330" s="5" t="n">
+        <v>7172000</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>23362</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="n">
+        <v>6024480</v>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>19624</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22311,7 +21895,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -22319,34 +21903,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H335" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I335" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H335" s="5" t="n">
+        <v>9451000</v>
+      </c>
+      <c r="I335" s="5" t="n">
+        <v>23164</v>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K335" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L335" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K335" s="5" t="n">
+        <v>7938840</v>
+      </c>
+      <c r="L335" s="5" t="n">
+        <v>19458</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22505,7 +22081,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -22513,34 +22089,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H338" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I338" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H338" s="5" t="n">
+        <v>7150000</v>
+      </c>
+      <c r="I338" s="5" t="n">
+        <v>23290</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K338" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L338" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K338" s="5" t="n">
+        <v>6006000</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>19564</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N338" s="3" t="inlineStr">
@@ -22761,7 +22329,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -22769,34 +22337,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H342" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I342" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H342" s="5" t="n">
+        <v>11703000</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>24742</v>
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K342" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L342" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K342" s="5" t="n">
+        <v>9830520</v>
+      </c>
+      <c r="L342" s="5" t="n">
+        <v>20783</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22831,7 +22391,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -22839,34 +22399,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H343" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I343" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H343" s="5" t="n">
+        <v>9451000</v>
+      </c>
+      <c r="I343" s="5" t="n">
+        <v>23164</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K343" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L343" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K343" s="5" t="n">
+        <v>7938840</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>19458</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N343" s="3" t="inlineStr">
@@ -23025,7 +22577,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -23033,34 +22585,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H346" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I346" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H346" s="5" t="n">
+        <v>7150000</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>23290</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K346" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L346" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K346" s="5" t="n">
+        <v>6006000</v>
+      </c>
+      <c r="L346" s="5" t="n">
+        <v>19564</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23157,7 +22701,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -23165,34 +22709,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H348" s="5" t="n">
+        <v>7022000</v>
+      </c>
+      <c r="I348" s="5" t="n">
+        <v>22435</v>
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K348" s="5" t="n">
+        <v>5898480</v>
+      </c>
+      <c r="L348" s="5" t="n">
+        <v>18845</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23351,7 +22887,7 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -23359,34 +22895,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H351" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I351" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H351" s="5" t="n">
+        <v>9339000</v>
+      </c>
+      <c r="I351" s="5" t="n">
+        <v>22890</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K351" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L351" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K351" s="5" t="n">
+        <v>7844760</v>
+      </c>
+      <c r="L351" s="5" t="n">
+        <v>19227</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N351" s="3" t="inlineStr">
@@ -23545,7 +23073,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -23553,34 +23081,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H354" s="5" t="n">
+        <v>7108000</v>
+      </c>
+      <c r="I354" s="5" t="n">
+        <v>23153</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K354" s="5" t="n">
+        <v>5970720</v>
+      </c>
+      <c r="L354" s="5" t="n">
+        <v>19449</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -23863,7 +23383,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -23871,34 +23391,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H359" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I359" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H359" s="5" t="n">
+        <v>9245000</v>
+      </c>
+      <c r="I359" s="5" t="n">
+        <v>22659</v>
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K359" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L359" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K359" s="5" t="n">
+        <v>7765800</v>
+      </c>
+      <c r="L359" s="5" t="n">
+        <v>19034</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -24057,7 +23569,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -24065,34 +23577,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H362" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I362" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H362" s="5" t="n">
+        <v>7060000</v>
+      </c>
+      <c r="I362" s="5" t="n">
+        <v>22922</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K362" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L362" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K362" s="5" t="n">
+        <v>5930400</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>19255</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N362" s="3" t="inlineStr">
@@ -24189,7 +23693,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -24197,34 +23701,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H364" s="5" t="n">
+        <v>6910000</v>
+      </c>
+      <c r="I364" s="5" t="n">
+        <v>22077</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>5804400</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>18544</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
@@ -24383,7 +23879,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -24391,34 +23887,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H367" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I367" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H367" s="5" t="n">
+        <v>9060000</v>
+      </c>
+      <c r="I367" s="5" t="n">
+        <v>22206</v>
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K367" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L367" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K367" s="5" t="n">
+        <v>7610400</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>18653</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N367" s="3" t="inlineStr">
@@ -24577,7 +24065,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -24585,34 +24073,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H370" s="5" t="n">
+        <v>7038000</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>22851</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K370" s="5" t="n">
+        <v>5911920</v>
+      </c>
+      <c r="L370" s="5" t="n">
+        <v>19195</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -24709,7 +24189,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -24717,34 +24197,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H372" s="5" t="n">
+        <v>6890000</v>
+      </c>
+      <c r="I372" s="5" t="n">
+        <v>22013</v>
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K372" s="5" t="n">
+        <v>5787600</v>
+      </c>
+      <c r="L372" s="5" t="n">
+        <v>18491</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -24903,7 +24375,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -24911,34 +24383,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H375" s="5" t="n">
+        <v>9033000</v>
+      </c>
+      <c r="I375" s="5" t="n">
+        <v>22140</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K375" s="5" t="n">
+        <v>7587720</v>
+      </c>
+      <c r="L375" s="5" t="n">
+        <v>18597</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N375" s="3" t="inlineStr">
@@ -25097,7 +24561,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -25105,34 +24569,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H378" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I378" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H378" s="5" t="n">
+        <v>7017000</v>
+      </c>
+      <c r="I378" s="5" t="n">
+        <v>22782</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K378" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L378" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K378" s="5" t="n">
+        <v>5894280</v>
+      </c>
+      <c r="L378" s="5" t="n">
+        <v>19137</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -25415,7 +24871,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -25423,34 +24879,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H383" s="5" t="n">
+        <v>9006000</v>
+      </c>
+      <c r="I383" s="5" t="n">
+        <v>22074</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K383" s="5" t="n">
+        <v>7565040</v>
+      </c>
+      <c r="L383" s="5" t="n">
+        <v>18542</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -25609,7 +25057,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -25617,34 +25065,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H386" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I386" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H386" s="5" t="n">
+        <v>6996000</v>
+      </c>
+      <c r="I386" s="5" t="n">
+        <v>22714</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K386" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L386" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K386" s="5" t="n">
+        <v>5876640</v>
+      </c>
+      <c r="L386" s="5" t="n">
+        <v>19080</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N386" s="3" t="inlineStr">
@@ -25927,7 +25367,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -25935,34 +25375,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H391" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I391" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H391" s="5" t="n">
+        <v>8979000</v>
+      </c>
+      <c r="I391" s="5" t="n">
+        <v>22007</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K391" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L391" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K391" s="5" t="n">
+        <v>7542360</v>
+      </c>
+      <c r="L391" s="5" t="n">
+        <v>18486</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N391" s="3" t="inlineStr">
@@ -26121,7 +25553,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -26129,34 +25561,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H394" s="5" t="n">
+        <v>6975000</v>
+      </c>
+      <c r="I394" s="5" t="n">
+        <v>22646</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K394" s="5" t="n">
+        <v>5859000</v>
+      </c>
+      <c r="L394" s="5" t="n">
+        <v>19023</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26439,7 +25863,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -26447,34 +25871,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H399" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I399" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H399" s="5" t="n">
+        <v>8952000</v>
+      </c>
+      <c r="I399" s="5" t="n">
+        <v>21941</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K399" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L399" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K399" s="5" t="n">
+        <v>7519680</v>
+      </c>
+      <c r="L399" s="5" t="n">
+        <v>18431</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N399" s="3" t="inlineStr">
@@ -26633,7 +26049,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -26641,34 +26057,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H402" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I402" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H402" s="5" t="n">
+        <v>6954000</v>
+      </c>
+      <c r="I402" s="5" t="n">
+        <v>22578</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K402" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L402" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K402" s="5" t="n">
+        <v>5841360</v>
+      </c>
+      <c r="L402" s="5" t="n">
+        <v>18965</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">
@@ -26951,7 +26359,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -26959,34 +26367,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H407" s="5" t="n">
+        <v>8952000</v>
+      </c>
+      <c r="I407" s="5" t="n">
+        <v>21941</v>
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K407" s="5" t="n">
+        <v>7519680</v>
+      </c>
+      <c r="L407" s="5" t="n">
+        <v>18431</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N407" s="3" t="inlineStr">
@@ -27145,7 +26545,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -27153,34 +26553,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H410" s="5" t="n">
+        <v>6954000</v>
+      </c>
+      <c r="I410" s="5" t="n">
+        <v>22578</v>
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K410" s="5" t="n">
+        <v>5841360</v>
+      </c>
+      <c r="L410" s="5" t="n">
+        <v>18965</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N410" s="3" t="inlineStr">
@@ -27277,7 +26669,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -27285,34 +26677,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H412" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I412" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H412" s="5" t="n">
+        <v>6807000</v>
+      </c>
+      <c r="I412" s="5" t="n">
+        <v>21748</v>
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K412" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L412" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K412" s="5" t="n">
+        <v>5717880</v>
+      </c>
+      <c r="L412" s="5" t="n">
+        <v>18268</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N412" s="3" t="inlineStr">
@@ -27471,7 +26855,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -27479,34 +26863,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H415" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I415" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H415" s="5" t="n">
+        <v>8899000</v>
+      </c>
+      <c r="I415" s="5" t="n">
+        <v>21811</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K415" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L415" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K415" s="5" t="n">
+        <v>7475160</v>
+      </c>
+      <c r="L415" s="5" t="n">
+        <v>18321</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N415" s="3" t="inlineStr">
@@ -27665,7 +27041,7 @@
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -27673,34 +27049,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H418" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I418" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H418" s="5" t="n">
+        <v>6913000</v>
+      </c>
+      <c r="I418" s="5" t="n">
+        <v>22445</v>
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K418" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L418" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K418" s="5" t="n">
+        <v>5806920</v>
+      </c>
+      <c r="L418" s="5" t="n">
+        <v>18854</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
@@ -27983,7 +27351,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -27991,34 +27359,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H423" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I423" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H423" s="5" t="n">
+        <v>8872000</v>
+      </c>
+      <c r="I423" s="5" t="n">
+        <v>21745</v>
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K423" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L423" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K423" s="5" t="n">
+        <v>7452480</v>
+      </c>
+      <c r="L423" s="5" t="n">
+        <v>18266</v>
       </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N423" s="3" t="inlineStr">
@@ -28177,7 +27537,7 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -28185,34 +27545,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H426" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I426" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H426" s="5" t="n">
+        <v>6892000</v>
+      </c>
+      <c r="I426" s="5" t="n">
+        <v>22377</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K426" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L426" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K426" s="5" t="n">
+        <v>5789280</v>
+      </c>
+      <c r="L426" s="5" t="n">
+        <v>18796</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N426" s="3" t="inlineStr">
@@ -28495,7 +27847,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -28503,34 +27855,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H431" s="5" t="n">
+        <v>8845000</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>21679</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K431" s="5" t="n">
+        <v>7429800</v>
+      </c>
+      <c r="L431" s="5" t="n">
+        <v>18210</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N431" s="3" t="inlineStr">
@@ -28689,7 +28033,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -28697,34 +28041,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H434" s="5" t="n">
+        <v>6871000</v>
+      </c>
+      <c r="I434" s="5" t="n">
+        <v>22308</v>
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K434" s="5" t="n">
+        <v>5771640</v>
+      </c>
+      <c r="L434" s="5" t="n">
+        <v>18739</v>
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N434" s="3" t="inlineStr">
@@ -29007,7 +28343,7 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -29015,34 +28351,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H439" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I439" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H439" s="5" t="n">
+        <v>8819000</v>
+      </c>
+      <c r="I439" s="5" t="n">
+        <v>21615</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K439" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L439" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K439" s="5" t="n">
+        <v>7407960</v>
+      </c>
+      <c r="L439" s="5" t="n">
+        <v>18157</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N439" s="3" t="inlineStr">
@@ -29201,7 +28529,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -29209,34 +28537,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H442" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I442" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H442" s="5" t="n">
+        <v>6851000</v>
+      </c>
+      <c r="I442" s="5" t="n">
+        <v>22244</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K442" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L442" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K442" s="5" t="n">
+        <v>5754840</v>
+      </c>
+      <c r="L442" s="5" t="n">
+        <v>18685</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N442" s="3" t="inlineStr">
@@ -29519,7 +28839,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -29527,34 +28847,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H447" s="5" t="n">
+        <v>8792000</v>
+      </c>
+      <c r="I447" s="5" t="n">
+        <v>21549</v>
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K447" s="5" t="n">
+        <v>7385280</v>
+      </c>
+      <c r="L447" s="5" t="n">
+        <v>18101</v>
       </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N447" s="3" t="inlineStr">
@@ -29713,7 +29025,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -29721,34 +29033,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H450" s="5" t="n">
+        <v>6830000</v>
+      </c>
+      <c r="I450" s="5" t="n">
+        <v>22175</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K450" s="5" t="n">
+        <v>5737200</v>
+      </c>
+      <c r="L450" s="5" t="n">
+        <v>18627</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N450" s="3" t="inlineStr">
@@ -30031,7 +29335,7 @@
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr">
@@ -30039,34 +29343,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H455" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I455" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H455" s="5" t="n">
+        <v>8766000</v>
+      </c>
+      <c r="I455" s="5" t="n">
+        <v>21485</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K455" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L455" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K455" s="5" t="n">
+        <v>7363440</v>
+      </c>
+      <c r="L455" s="5" t="n">
+        <v>18048</v>
       </c>
       <c r="M455" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N455" s="3" t="inlineStr">
@@ -30225,7 +29521,7 @@
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
@@ -30233,34 +29529,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H458" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I458" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H458" s="5" t="n">
+        <v>6810000</v>
+      </c>
+      <c r="I458" s="5" t="n">
+        <v>22110</v>
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K458" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L458" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K458" s="5" t="n">
+        <v>5720400</v>
+      </c>
+      <c r="L458" s="5" t="n">
+        <v>18573</v>
       </c>
       <c r="M458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N458" s="3" t="inlineStr">
@@ -30357,7 +29645,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -30365,34 +29653,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H460" s="5" t="n">
+        <v>6665000</v>
+      </c>
+      <c r="I460" s="5" t="n">
+        <v>21294</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K460" s="5" t="n">
+        <v>5598600</v>
+      </c>
+      <c r="L460" s="5" t="n">
+        <v>17887</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N460" s="3" t="inlineStr">
@@ -30551,7 +29831,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -30559,34 +29839,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H463" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I463" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H463" s="5" t="n">
+        <v>8740000</v>
+      </c>
+      <c r="I463" s="5" t="n">
+        <v>21422</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K463" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L463" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K463" s="5" t="n">
+        <v>7341600</v>
+      </c>
+      <c r="L463" s="5" t="n">
+        <v>17994</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N463" s="3" t="inlineStr">
@@ -30745,7 +30017,7 @@
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
@@ -30753,34 +30025,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H466" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I466" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H466" s="5" t="n">
+        <v>6789000</v>
+      </c>
+      <c r="I466" s="5" t="n">
+        <v>22042</v>
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K466" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L466" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K466" s="5" t="n">
+        <v>5702760</v>
+      </c>
+      <c r="L466" s="5" t="n">
+        <v>18515</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N466" s="3" t="inlineStr">
@@ -31063,7 +30327,7 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -31071,34 +30335,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H471" s="5" t="n">
+        <v>8740000</v>
+      </c>
+      <c r="I471" s="5" t="n">
+        <v>21422</v>
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K471" s="5" t="n">
+        <v>7341600</v>
+      </c>
+      <c r="L471" s="5" t="n">
+        <v>17994</v>
       </c>
       <c r="M471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N471" s="3" t="inlineStr">
@@ -31257,7 +30513,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -31265,34 +30521,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H474" s="5" t="n">
+        <v>6789000</v>
+      </c>
+      <c r="I474" s="5" t="n">
+        <v>22042</v>
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K474" s="5" t="n">
+        <v>5702760</v>
+      </c>
+      <c r="L474" s="5" t="n">
+        <v>18515</v>
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N474" s="3" t="inlineStr">
@@ -31575,7 +30823,7 @@
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr">
@@ -31583,34 +30831,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H479" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I479" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H479" s="5" t="n">
+        <v>8687000</v>
+      </c>
+      <c r="I479" s="5" t="n">
+        <v>21292</v>
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K479" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L479" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K479" s="5" t="n">
+        <v>7297080</v>
+      </c>
+      <c r="L479" s="5" t="n">
+        <v>17885</v>
       </c>
       <c r="M479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N479" s="3" t="inlineStr">
@@ -31769,7 +31009,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -31777,34 +31017,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H482" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I482" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H482" s="5" t="n">
+        <v>6748000</v>
+      </c>
+      <c r="I482" s="5" t="n">
+        <v>21909</v>
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K482" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L482" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K482" s="5" t="n">
+        <v>5668320</v>
+      </c>
+      <c r="L482" s="5" t="n">
+        <v>18404</v>
       </c>
       <c r="M482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N482" s="3" t="inlineStr">
@@ -32087,7 +31319,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -32095,34 +31327,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H487" s="5" t="n">
+        <v>8661000</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>21228</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K487" s="5" t="n">
+        <v>7275240</v>
+      </c>
+      <c r="L487" s="5" t="n">
+        <v>17831</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N487" s="3" t="inlineStr">
@@ -32281,7 +31505,7 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -32289,34 +31513,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H490" s="5" t="n">
+        <v>6681000</v>
+      </c>
+      <c r="I490" s="5" t="n">
+        <v>21692</v>
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K490" s="5" t="n">
+        <v>5612040</v>
+      </c>
+      <c r="L490" s="5" t="n">
+        <v>18221</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -32599,7 +31815,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -32607,34 +31823,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H495" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I495" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H495" s="5" t="n">
+        <v>8640000</v>
+      </c>
+      <c r="I495" s="5" t="n">
+        <v>21176</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K495" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L495" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K495" s="5" t="n">
+        <v>7257600</v>
+      </c>
+      <c r="L495" s="5" t="n">
+        <v>17788</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N495" s="3" t="inlineStr">
@@ -32793,7 +32001,7 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -32801,34 +32009,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H498" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I498" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H498" s="5" t="n">
+        <v>6594000</v>
+      </c>
+      <c r="I498" s="5" t="n">
+        <v>21409</v>
       </c>
       <c r="J498" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K498" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L498" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K498" s="5" t="n">
+        <v>5538960</v>
+      </c>
+      <c r="L498" s="5" t="n">
+        <v>17984</v>
       </c>
       <c r="M498" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N498" s="3" t="inlineStr">
@@ -33661,22 +32861,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -35003,12 +34203,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
+$1439万
+$25,785/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -35050,20 +34250,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
+$1432万
+$25,656/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1671万
+$24,579/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -35097,20 +34297,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
+$1424万
+$25,527/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1663万
+$24,457/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -35144,20 +34344,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
+$1403万
+$25,143/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1638万
+$24,090/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -35191,20 +34391,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
+$1389万
+$24,892/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1622万
+$23,849/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -35238,20 +34438,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
+$1368万
+$24,520/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1614万
+$23,729/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -35285,20 +34485,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
+$1341万
+$24,029/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1581万
+$23,256/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -35332,20 +34532,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr">
+$1341万
+$24,029/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1581万
+$23,256/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -35379,20 +34579,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
+$1327万
+$23,789/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1566万
+$23,022/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -35426,20 +34626,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
+$1321万
+$23,670/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1558万
+$22,907/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
@@ -35473,20 +34673,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
+$1314万
+$23,548/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
--
--
-(待售)</t>
+$1550万
+$22,791/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
@@ -35626,22 +34826,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -35793,12 +34993,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$797万
+$25,951/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -35817,12 +35017,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1106万
+$27,115/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -35864,12 +35064,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$787万
+$25,642/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -35888,12 +35088,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1080万
+$26,478/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -35935,12 +35135,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$767万
+$24,993/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -35959,12 +35159,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1047万
+$25,657/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -36006,12 +35206,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$760万
+$24,746/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -36030,12 +35230,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1036万
+$25,404/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -36077,12 +35277,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$752万
+$24,502/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -36101,12 +35301,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1026万
+$25,152/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -36148,12 +35348,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$745万
+$24,257/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -36172,12 +35372,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1016万
+$24,904/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -36219,12 +35419,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$737万
+$24,020/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -36243,12 +35443,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1006万
+$24,657/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -36290,12 +35490,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$735万
+$23,948/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -36314,12 +35514,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$996万
+$24,412/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -36361,12 +35561,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$735万
+$23,948/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -36385,12 +35585,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$996万
+$24,412/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -36432,12 +35632,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$731万
+$23,805/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -36456,12 +35656,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$984万
+$24,123/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -36503,12 +35703,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$728万
+$23,713/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -36527,12 +35727,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$978万
+$23,980/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -36574,12 +35774,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$726万
+$23,642/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -36598,12 +35798,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$972万
+$23,836/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -36645,12 +35845,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$724万
+$23,573/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -36669,12 +35869,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$967万
+$23,694/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -36716,12 +35916,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$722万
+$23,502/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -36740,12 +35940,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$961万
+$23,554/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -36787,12 +35987,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$719万
+$23,430/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -36811,12 +36011,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$955万
+$23,412/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -36858,12 +36058,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$717万
+$23,362/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -36882,12 +36082,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$950万
+$23,272/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36929,12 +36129,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$715万
+$23,290/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -36953,12 +36153,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$945万
+$23,164/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -36984,12 +36184,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
--
--
-(待售)</t>
+$702万
+$22,435/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -37000,12 +36200,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$715万
+$23,290/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -37024,20 +36224,20 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+$945万
+$23,164/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>H | 473呎 (2房)
--
--
-(待售)</t>
+$1170万
+$24,742/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -37071,12 +36271,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
--
--
-(待售)</t>
+$711万
+$23,153/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -37095,12 +36295,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$934万
+$22,890/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -37126,12 +36326,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
--
--
-(待售)</t>
+$691万
+$22,077/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -37142,12 +36342,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$706万
+$22,922/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -37166,12 +36366,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$924万
+$22,659/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -37197,12 +36397,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
--
--
-(待售)</t>
+$689万
+$22,013/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37213,12 +36413,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$704万
+$22,851/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -37237,12 +36437,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$906万
+$22,206/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -37284,12 +36484,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$702万
+$22,782/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -37308,12 +36508,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$903万
+$22,140/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -37355,12 +36555,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$700万
+$22,714/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -37379,12 +36579,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$901万
+$22,074/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -37426,12 +36626,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$698万
+$22,646/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -37450,12 +36650,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$898万
+$22,007/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -37497,12 +36697,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$695万
+$22,578/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -37521,12 +36721,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$895万
+$21,941/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -37552,12 +36752,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
--
--
-(待售)</t>
+$681万
+$21,748/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -37568,12 +36768,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$695万
+$22,578/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -37592,12 +36792,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$895万
+$21,941/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -37639,12 +36839,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$691万
+$22,445/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -37663,12 +36863,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$890万
+$21,811/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -37710,12 +36910,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$689万
+$22,377/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -37734,12 +36934,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$887万
+$21,745/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -37781,12 +36981,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$687万
+$22,308/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -37805,12 +37005,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$884万
+$21,679/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -37852,12 +37052,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$685万
+$22,244/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -37876,12 +37076,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$882万
+$21,615/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -37923,12 +37123,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$683万
+$22,175/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -37947,12 +37147,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$879万
+$21,549/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -37978,12 +37178,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
--
--
-(待售)</t>
+$666万
+$21,294/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -37994,12 +37194,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$681万
+$22,110/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -38018,12 +37218,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$877万
+$21,485/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -38065,12 +37265,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$679万
+$22,042/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -38089,12 +37289,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$874万
+$21,422/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -38136,12 +37336,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$679万
+$22,042/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -38160,12 +37360,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$874万
+$21,422/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -38207,12 +37407,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$675万
+$21,909/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -38231,12 +37431,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$869万
+$21,292/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I40" s="22" t="inlineStr">
@@ -38278,12 +37478,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$668万
+$21,692/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
@@ -38302,12 +37502,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H41" s="20" t="inlineStr">
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$866万
+$21,228/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I41" s="22" t="inlineStr">
@@ -38349,12 +37549,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
--
--
-(待售)</t>
+$659万
+$21,409/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
@@ -38373,12 +37573,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$864万
+$21,176/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I42" s="22" t="inlineStr">

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,18 +117,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -207,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,16 +261,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +759,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -777,12 +769,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -792,12 +784,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -837,7 +829,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -847,12 +839,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -862,12 +854,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -877,7 +869,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -907,7 +899,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -917,12 +909,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -932,12 +924,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -947,7 +939,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -977,7 +969,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -987,12 +979,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1002,12 +994,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1017,7 +1009,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1039,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1057,12 +1049,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1072,12 +1064,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1087,7 +1079,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1241,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1259,12 +1251,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1274,12 +1266,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1289,7 +1281,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1373,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1391,12 +1383,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1406,12 +1398,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1421,7 +1413,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1575,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1593,12 +1585,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1608,12 +1600,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1623,7 +1615,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1707,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1725,12 +1717,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1740,12 +1732,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1755,7 +1747,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1909,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1927,12 +1919,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1942,12 +1934,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1957,7 +1949,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2235,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2253,12 +2245,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2268,12 +2260,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2283,7 +2275,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2561,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2579,12 +2571,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2594,12 +2586,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2609,7 +2601,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2887,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2905,12 +2897,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2920,12 +2912,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -2935,7 +2927,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3151,38 +3143,30 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>17238000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>25500</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K39" s="5" t="n">
+        <v>17238000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>25500</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3175,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3205,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3231,12 +3215,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3246,12 +3230,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3261,7 +3245,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3523,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3549,12 +3533,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3564,12 +3548,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3579,7 +3563,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3795,38 +3779,30 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>17102800</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>25300</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K49" s="5" t="n">
+        <v>17102800</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>25300</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3835,7 +3811,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3841,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3875,12 +3851,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3890,12 +3866,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -3905,7 +3881,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4121,38 +4097,30 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>17035200</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>25200</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K54" s="5" t="n">
+        <v>17035200</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>25200</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4161,7 +4129,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4159,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4201,12 +4169,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4216,12 +4184,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4231,7 +4199,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4485,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4527,12 +4495,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4542,12 +4510,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4557,7 +4525,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9407,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9449,12 +9417,12 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
@@ -9464,12 +9432,12 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
@@ -9479,7 +9447,7 @@
       </c>
       <c r="N139" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12763,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -12805,12 +12773,12 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr">
@@ -12820,12 +12788,12 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
@@ -12835,7 +12803,7 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13081,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13123,12 +13091,12 @@
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr">
@@ -13138,12 +13106,12 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
@@ -13153,7 +13121,7 @@
       </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13151,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13193,12 +13161,12 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -13208,12 +13176,12 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
@@ -13223,7 +13191,7 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13221,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -13263,12 +13231,12 @@
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr">
@@ -13278,12 +13246,12 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
@@ -13293,7 +13261,7 @@
       </c>
       <c r="N200" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13291,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -13333,12 +13301,12 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr">
@@ -13348,12 +13316,12 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
@@ -13363,7 +13331,7 @@
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13361,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -13403,12 +13371,12 @@
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr">
@@ -13418,12 +13386,12 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
@@ -13433,7 +13401,7 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13431,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -13473,12 +13441,12 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J203" s="3" t="inlineStr">
@@ -13488,12 +13456,12 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
@@ -13503,7 +13471,7 @@
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13501,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -13543,12 +13511,12 @@
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J204" s="3" t="inlineStr">
@@ -13558,12 +13526,12 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
@@ -13573,7 +13541,7 @@
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13603,7 +13571,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -13613,12 +13581,12 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J205" s="3" t="inlineStr">
@@ -13628,12 +13596,12 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
@@ -13643,7 +13611,7 @@
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32087,7 +32055,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -32097,12 +32065,12 @@
       </c>
       <c r="H503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J503" s="3" t="inlineStr">
@@ -32112,12 +32080,12 @@
       </c>
       <c r="K503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M503" s="3" t="inlineStr">
@@ -32127,7 +32095,7 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32125,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -32167,12 +32135,12 @@
       </c>
       <c r="H504" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I504" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J504" s="3" t="inlineStr">
@@ -32182,12 +32150,12 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M504" s="3" t="inlineStr">
@@ -32197,7 +32165,7 @@
       </c>
       <c r="N504" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32195,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -32237,12 +32205,12 @@
       </c>
       <c r="H505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J505" s="3" t="inlineStr">
@@ -32252,12 +32220,12 @@
       </c>
       <c r="K505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M505" s="3" t="inlineStr">
@@ -32267,7 +32235,7 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32297,7 +32265,7 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -32307,12 +32275,12 @@
       </c>
       <c r="H506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J506" s="3" t="inlineStr">
@@ -32322,12 +32290,12 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M506" s="3" t="inlineStr">
@@ -32337,7 +32305,7 @@
       </c>
       <c r="N506" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32367,7 +32335,7 @@
       </c>
       <c r="F507" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr">
@@ -32377,12 +32345,12 @@
       </c>
       <c r="H507" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I507" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J507" s="3" t="inlineStr">
@@ -32392,12 +32360,12 @@
       </c>
       <c r="K507" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L507" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M507" s="3" t="inlineStr">
@@ -32407,7 +32375,7 @@
       </c>
       <c r="N507" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32437,7 +32405,7 @@
       </c>
       <c r="F508" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
@@ -32447,12 +32415,12 @@
       </c>
       <c r="H508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J508" s="3" t="inlineStr">
@@ -32462,12 +32430,12 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M508" s="3" t="inlineStr">
@@ -32477,7 +32445,7 @@
       </c>
       <c r="N508" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32475,7 @@
       </c>
       <c r="F509" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G509" s="3" t="inlineStr">
@@ -32517,12 +32485,12 @@
       </c>
       <c r="H509" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I509" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J509" s="3" t="inlineStr">
@@ -32532,12 +32500,12 @@
       </c>
       <c r="K509" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L509" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M509" s="3" t="inlineStr">
@@ -32547,7 +32515,7 @@
       </c>
       <c r="N509" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32624,7 +32592,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32634,7 +32602,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32644,7 +32612,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -32689,41 +32657,41 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32736,9 +32704,9 @@
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -32752,12 +32720,12 @@
       <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -32783,9 +32751,9 @@
       <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -32799,12 +32767,12 @@
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -32846,12 +32814,12 @@
       <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -32893,12 +32861,12 @@
       <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -32940,12 +32908,12 @@
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -32987,12 +32955,12 @@
       <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33034,12 +33002,200 @@
       <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+$1724万
+$25,500/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+$859万
+$20,305/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 655呎 (3房)
+$1259万
+$19,226/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+$864万
+$19,453/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+$1866万
+$27,609/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+$931万
+$22,017/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 655呎 (3房)
+$1371万
+$20,931/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+$940万
+$21,180/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+$1710万
+$25,300/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+$931万
+$22,017/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 655呎 (3房)
+$1363万
+$20,806/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+$935万
+$21,054/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+$1704万
+$25,200/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+$920万
+$21,754/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 655呎 (3房)
+$1296万
+$19,786/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+$848万
+$19,110/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
 招标单位
@@ -33047,194 +33203,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
-$859万
-$20,305/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 655呎 (3房)
-$1259万
-$19,226/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
-$864万
-$19,453/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
-$1866万
-$27,609/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
-$931万
-$22,017/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>A | 655呎 (3房)
-$1371万
-$20,931/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
-$940万
-$21,180/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
-$931万
-$22,017/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>A | 655呎 (3房)
-$1363万
-$20,806/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
-$935万
-$21,054/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
-$920万
-$21,754/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 655呎 (3房)
-$1296万
-$19,786/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
-$848万
-$19,110/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
@@ -33313,7 +33281,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -33548,7 +33516,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
 招标单位
@@ -33971,7 +33939,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1439万
@@ -33982,9 +33950,9 @@
       <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -34018,7 +33986,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1432万
@@ -34026,7 +33994,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1671万
@@ -34065,7 +34033,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1424万
@@ -34073,7 +34041,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1663万
@@ -34112,7 +34080,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1403万
@@ -34120,7 +34088,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1638万
@@ -34159,7 +34127,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1389万
@@ -34167,7 +34135,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1622万
@@ -34206,7 +34174,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1368万
@@ -34214,7 +34182,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1614万
@@ -34253,7 +34221,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1341万
@@ -34261,7 +34229,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1581万
@@ -34300,7 +34268,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1341万
@@ -34308,7 +34276,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1581万
@@ -34347,7 +34315,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1327万
@@ -34355,7 +34323,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1566万
@@ -34394,7 +34362,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1321万
@@ -34402,7 +34370,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1558万
@@ -34441,7 +34409,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1314万
@@ -34449,7 +34417,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1550万
@@ -34507,9 +34475,9 @@
       <c r="F43" s="20" t="inlineStr">
         <is>
           <t>E | 383呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34589,27 +34557,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
@@ -34669,65 +34637,65 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 313呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 313呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 306呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 306呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 418呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 450呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 473呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>E | 418呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>F | 450呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>H | 473呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34729,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $797万
@@ -34785,7 +34753,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1106万
@@ -34832,7 +34800,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $787万
@@ -34856,7 +34824,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1080万
@@ -34903,7 +34871,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $767万
@@ -34927,7 +34895,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1047万
@@ -34974,7 +34942,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $760万
@@ -34998,7 +34966,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1036万
@@ -35045,7 +35013,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $752万
@@ -35069,7 +35037,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1026万
@@ -35116,7 +35084,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $745万
@@ -35140,7 +35108,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1016万
@@ -35187,7 +35155,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $737万
@@ -35211,7 +35179,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1006万
@@ -35258,7 +35226,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $735万
@@ -35282,7 +35250,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $996万
@@ -35329,7 +35297,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $735万
@@ -35353,7 +35321,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $996万
@@ -35400,7 +35368,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $731万
@@ -35424,7 +35392,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $984万
@@ -35471,7 +35439,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $728万
@@ -35495,7 +35463,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $978万
@@ -35542,7 +35510,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $726万
@@ -35566,7 +35534,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $972万
@@ -35613,7 +35581,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $724万
@@ -35637,7 +35605,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $967万
@@ -35684,7 +35652,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $722万
@@ -35708,7 +35676,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $961万
@@ -35755,7 +35723,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $719万
@@ -35779,7 +35747,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $955万
@@ -35826,7 +35794,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $717万
@@ -35850,7 +35818,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $950万
@@ -35897,7 +35865,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $715万
@@ -35921,7 +35889,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $945万
@@ -35952,7 +35920,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $702万
@@ -35968,7 +35936,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $715万
@@ -35992,7 +35960,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $945万
@@ -36000,7 +35968,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 473呎 (2房)
 $1170万
@@ -36039,7 +36007,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $711万
@@ -36063,7 +36031,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $934万
@@ -36094,7 +36062,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $691万
@@ -36110,7 +36078,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $706万
@@ -36134,7 +36102,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $924万
@@ -36165,7 +36133,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $689万
@@ -36181,7 +36149,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $704万
@@ -36205,7 +36173,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $906万
@@ -36252,7 +36220,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $702万
@@ -36276,7 +36244,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $903万
@@ -36323,7 +36291,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $700万
@@ -36347,7 +36315,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $901万
@@ -36394,7 +36362,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $698万
@@ -36418,7 +36386,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $898万
@@ -36465,7 +36433,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $695万
@@ -36489,7 +36457,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $895万
@@ -36520,7 +36488,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $681万
@@ -36536,7 +36504,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $695万
@@ -36560,7 +36528,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $895万
@@ -36607,7 +36575,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $691万
@@ -36631,7 +36599,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $890万
@@ -36678,7 +36646,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $689万
@@ -36702,7 +36670,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $887万
@@ -36749,7 +36717,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $687万
@@ -36773,7 +36741,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $884万
@@ -36820,7 +36788,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $685万
@@ -36844,7 +36812,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $882万
@@ -36891,7 +36859,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $683万
@@ -36915,7 +36883,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H36" s="23" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $879万
@@ -36946,7 +36914,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $666万
@@ -36962,7 +36930,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $681万
@@ -36986,7 +36954,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $877万
@@ -37033,7 +37001,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $679万
@@ -37057,7 +37025,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $874万
@@ -37104,7 +37072,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $679万
@@ -37128,7 +37096,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $874万
@@ -37175,7 +37143,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $675万
@@ -37199,7 +37167,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H40" s="23" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $869万
@@ -37246,7 +37214,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $668万
@@ -37270,7 +37238,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $866万
@@ -37317,7 +37285,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $659万
@@ -37341,7 +37309,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $864万
@@ -37367,57 +37335,57 @@
       <c r="B43" s="20" t="inlineStr">
         <is>
           <t>A | 634呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 276呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>B | 276呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 267呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>C | 267呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 411呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>G | 373呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>F | 411呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>G | 373呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I43" s="21" t="inlineStr">

--- a/web/files/九龙-深水埗-叡璟I.xlsx
+++ b/web/files/九龙-深水埗-叡璟I.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +126,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -202,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,9 +260,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9477,7 +9469,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9725,7 +9717,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -9787,7 +9779,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10035,7 +10027,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10097,7 +10089,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10345,7 +10337,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10407,7 +10399,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10655,7 +10647,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -10717,7 +10709,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -10965,7 +10957,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11027,7 +11019,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11275,7 +11267,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11337,7 +11329,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -11585,7 +11577,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11647,7 +11639,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -11895,7 +11887,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -11957,7 +11949,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12205,7 +12197,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -12267,7 +12259,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12515,7 +12507,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12577,7 +12569,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13703,7 +13695,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -13889,7 +13881,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14199,7 +14191,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14385,7 +14377,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14695,7 +14687,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -14881,7 +14873,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15191,7 +15183,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15377,7 +15369,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15687,7 +15679,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -15873,7 +15865,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16183,7 +16175,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16369,7 +16361,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16679,7 +16671,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16865,7 +16857,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -17175,7 +17167,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17361,7 +17353,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17671,7 +17663,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17857,7 +17849,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -18167,7 +18159,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -18353,7 +18345,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -18663,7 +18655,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18849,7 +18841,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -19159,7 +19151,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -19345,7 +19337,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -19655,7 +19647,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -19841,7 +19833,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -20151,7 +20143,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -20337,7 +20329,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -20647,7 +20639,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -20833,7 +20825,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -21143,7 +21135,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -21329,7 +21321,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -21639,7 +21631,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -21825,7 +21817,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -22073,7 +22065,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -22135,7 +22127,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -22321,7 +22313,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -22445,7 +22437,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -22631,7 +22623,7 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -22817,7 +22809,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -23127,7 +23119,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -23313,7 +23305,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -23437,7 +23429,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -23623,7 +23615,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -23809,7 +23801,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -23933,7 +23925,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -24119,7 +24111,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -24305,7 +24297,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -24615,7 +24607,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -24801,7 +24793,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -25111,7 +25103,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -25297,7 +25289,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -25607,7 +25599,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -25793,7 +25785,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -26103,7 +26095,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -26289,7 +26281,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -26413,7 +26405,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -26599,7 +26591,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -26785,7 +26777,7 @@
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -27095,7 +27087,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -27281,7 +27273,7 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -27591,7 +27583,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -27777,7 +27769,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -28087,7 +28079,7 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -28273,7 +28265,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -28583,7 +28575,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -28769,7 +28761,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -29079,7 +29071,7 @@
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr">
@@ -29265,7 +29257,7 @@
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
@@ -29389,7 +29381,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -29575,7 +29567,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -29761,7 +29753,7 @@
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
@@ -30071,7 +30063,7 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -30257,7 +30249,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -30567,7 +30559,7 @@
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr">
@@ -30753,7 +30745,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -31063,7 +31055,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -31249,7 +31241,7 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -31559,7 +31551,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -31745,7 +31737,7 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -32592,12 +32584,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -33939,12 +33931,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1439万
 $25,785/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -33986,20 +33978,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1432万
 $25,656/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1671万
 $24,579/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -34033,20 +34025,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1424万
 $25,527/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1663万
 $24,457/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -34080,20 +34072,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1403万
 $25,143/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1638万
 $24,090/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -34127,20 +34119,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1389万
 $24,892/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E36" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1622万
 $23,849/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -34174,20 +34166,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1368万
 $24,520/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1614万
 $23,729/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -34221,20 +34213,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1341万
 $24,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1581万
 $23,256/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -34268,20 +34260,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1341万
 $24,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1581万
 $23,256/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -34315,20 +34307,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1327万
 $23,789/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E40" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1566万
 $23,022/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -34362,20 +34354,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1321万
 $23,670/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E41" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1558万
 $22,907/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -34409,20 +34401,20 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>C | 558呎 (3房)
 $1314万
 $23,548/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 680呎 (3房)
 $1550万
 $22,791/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
@@ -34557,12 +34549,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -34729,12 +34721,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $797万
 $25,951/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -34753,12 +34745,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1106万
 $27,115/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -34800,12 +34792,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $787万
 $25,642/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -34824,12 +34816,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1080万
 $26,478/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -34871,12 +34863,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $767万
 $24,993/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -34895,12 +34887,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1047万
 $25,657/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -34942,12 +34934,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $760万
 $24,746/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -34966,12 +34958,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1036万
 $25,404/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -35013,12 +35005,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $752万
 $24,502/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -35037,12 +35029,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1026万
 $25,152/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -35084,12 +35076,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $745万
 $24,257/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -35108,12 +35100,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1016万
 $24,904/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -35155,12 +35147,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $737万
 $24,020/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -35179,12 +35171,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1006万
 $24,657/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -35226,12 +35218,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $735万
 $23,948/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -35250,12 +35242,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $996万
 $24,412/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -35297,12 +35289,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $735万
 $23,948/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -35321,12 +35313,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $996万
 $24,412/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -35368,12 +35360,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $731万
 $23,805/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -35392,12 +35384,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $984万
 $24,123/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -35439,12 +35431,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $728万
 $23,713/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -35463,12 +35455,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $978万
 $23,980/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -35510,12 +35502,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $726万
 $23,642/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -35534,12 +35526,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $972万
 $23,836/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -35581,12 +35573,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $724万
 $23,573/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -35605,12 +35597,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $967万
 $23,694/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -35652,12 +35644,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $722万
 $23,502/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -35676,12 +35668,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $961万
 $23,554/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -35723,12 +35715,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $719万
 $23,430/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -35747,12 +35739,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $955万
 $23,412/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -35794,12 +35786,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $717万
 $23,362/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -35818,12 +35810,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $950万
 $23,272/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -35865,12 +35857,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $715万
 $23,290/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -35889,12 +35881,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $945万
 $23,164/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -35920,12 +35912,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $702万
 $22,435/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -35936,12 +35928,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $715万
 $23,290/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -35960,20 +35952,20 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $945万
 $23,164/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 473呎 (2房)
 $1170万
 $24,742/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36007,12 +35999,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $711万
 $23,153/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -36031,12 +36023,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $934万
 $22,890/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -36062,12 +36054,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $691万
 $22,077/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -36078,12 +36070,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $706万
 $22,922/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -36102,12 +36094,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $924万
 $22,659/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -36133,12 +36125,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $689万
 $22,013/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -36149,12 +36141,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $704万
 $22,851/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -36173,12 +36165,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $906万
 $22,206/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -36220,12 +36212,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $702万
 $22,782/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -36244,12 +36236,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $903万
 $22,140/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -36291,12 +36283,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $700万
 $22,714/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -36315,12 +36307,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $901万
 $22,074/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -36362,12 +36354,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $698万
 $22,646/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -36386,12 +36378,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $898万
 $22,007/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -36433,12 +36425,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $695万
 $22,578/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -36457,12 +36449,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $895万
 $21,941/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -36488,12 +36480,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $681万
 $21,748/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -36504,12 +36496,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $695万
 $22,578/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -36528,12 +36520,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $895万
 $21,941/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -36575,12 +36567,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $691万
 $22,445/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -36599,12 +36591,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $890万
 $21,811/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -36646,12 +36638,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $689万
 $22,377/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -36670,12 +36662,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $887万
 $21,745/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -36717,12 +36709,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $687万
 $22,308/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -36741,12 +36733,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $884万
 $21,679/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -36788,12 +36780,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $685万
 $22,244/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -36812,12 +36804,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $882万
 $21,615/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -36859,12 +36851,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $683万
 $22,175/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -36883,12 +36875,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $879万
 $21,549/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -36914,12 +36906,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
 $666万
 $21,294/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -36930,12 +36922,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $681万
 $22,110/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -36954,12 +36946,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $877万
 $21,485/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -37001,12 +36993,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $679万
 $22,042/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -37025,12 +37017,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $874万
 $21,422/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -37072,12 +37064,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $679万
 $22,042/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -37096,12 +37088,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $874万
 $21,422/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -37143,12 +37135,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $675万
 $21,909/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -37167,12 +37159,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $869万
 $21,292/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I40" s="21" t="inlineStr">
@@ -37214,12 +37206,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $668万
 $21,692/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -37238,12 +37230,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $866万
 $21,228/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -37285,12 +37277,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 308呎 (1房)
 $659万
 $21,409/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
@@ -37309,12 +37301,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $864万
 $21,176/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I42" s="21" t="inlineStr">
